--- a/data/07_QUARTERLY_WEIGHTING/2024/T4/444X_1D/LFS_SAMPLE_DATA_2024_T4_444X_1D_SUMMARY_OF_Xs_EST_DES_WEIGHT.xlsx
+++ b/data/07_QUARTERLY_WEIGHTING/2024/T4/444X_1D/LFS_SAMPLE_DATA_2024_T4_444X_1D_SUMMARY_OF_Xs_EST_DES_WEIGHT.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:QD4"/>
+  <dimension ref="A1:QD3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2593,2682 +2593,2681 @@
         </is>
       </c>
       <c r="B2">
-        <v>4408482.898452759</v>
+        <v>2435086.577816167</v>
       </c>
       <c r="C2">
-        <v>946009.4449157715</v>
+        <v>617097.8219488491</v>
       </c>
       <c r="D2">
-        <v>897245.6761169434</v>
+        <v>553058.3261356597</v>
       </c>
       <c r="E2">
-        <v>882639.2987060547</v>
+        <v>417616.0721064299</v>
       </c>
       <c r="F2">
-        <v>638032.8248291016</v>
+        <v>348636.2633479309</v>
       </c>
       <c r="G2">
-        <v>825098.6602020264</v>
+        <v>369271.1880225898</v>
       </c>
       <c r="H2">
-        <v>644199.4504241943</v>
+        <v>372976.6165509298</v>
       </c>
       <c r="I2">
-        <v>415112.5469360352</v>
+        <v>245730.2234402738</v>
       </c>
       <c r="J2">
-        <v>343486.3421783447</v>
+        <v>181342.2359124488</v>
       </c>
       <c r="K2">
-        <v>353102.7899017334</v>
+        <v>142837.4718534084</v>
       </c>
       <c r="L2">
-        <v>143393.4237518311</v>
+        <v>92009.33744812843</v>
       </c>
       <c r="M2">
-        <v>213671.2919616699</v>
+        <v>123319.6329647891</v>
       </c>
       <c r="N2">
-        <v>3829421.964439392</v>
+        <v>2028247.831144195</v>
       </c>
       <c r="O2">
-        <v>550929.4535179138</v>
+        <v>289113.8729801912</v>
       </c>
       <c r="P2">
-        <v>520574.638671875</v>
+        <v>304186.9462738459</v>
       </c>
       <c r="Q2">
-        <v>438195.7258605957</v>
+        <v>249148.3050379899</v>
       </c>
       <c r="R2">
-        <v>484588.8992881775</v>
+        <v>234501.2002687122</v>
       </c>
       <c r="S2">
-        <v>631632.0369148254</v>
+        <v>271550.5505709473</v>
       </c>
       <c r="T2">
-        <v>430043.5943450928</v>
+        <v>232246.34146675</v>
       </c>
       <c r="U2">
-        <v>310293.7313995361</v>
+        <v>186151.7943184116</v>
       </c>
       <c r="V2">
-        <v>274298.5526351929</v>
+        <v>138351.6975941383</v>
       </c>
       <c r="W2">
-        <v>139285.0891418457</v>
+        <v>88947.0143559572</v>
       </c>
       <c r="X2">
-        <v>149554.7839508057</v>
+        <v>93444.74756504585</v>
       </c>
       <c r="Y2">
-        <v>221991.7363967896</v>
+        <v>107974.1196508589</v>
       </c>
       <c r="Z2">
-        <v>4525323.142944336</v>
+        <v>2379789.993137228</v>
       </c>
       <c r="AA2">
-        <v>1158424.232330322</v>
+        <v>713605.3510025752</v>
       </c>
       <c r="AB2">
-        <v>1374761.134384155</v>
+        <v>714320.2934210722</v>
       </c>
       <c r="AC2">
-        <v>1046085.441375732</v>
+        <v>474842.2164412421</v>
       </c>
       <c r="AD2">
-        <v>714990.7503967285</v>
+        <v>429500.8705300601</v>
       </c>
       <c r="AE2">
-        <v>796465.666595459</v>
+        <v>436193.2225619344</v>
       </c>
       <c r="AF2">
-        <v>576441.471786499</v>
+        <v>326884.009823251</v>
       </c>
       <c r="AG2">
-        <v>428589.2324676514</v>
+        <v>247075.4326166104</v>
       </c>
       <c r="AH2">
-        <v>246707.7724914551</v>
+        <v>157783.0028769656</v>
       </c>
       <c r="AI2">
-        <v>173584.4572906494</v>
+        <v>117515.0096540628</v>
       </c>
       <c r="AJ2">
-        <v>159965.2857208252</v>
+        <v>97289.58699739751</v>
       </c>
       <c r="AK2">
-        <v>197670.8505096436</v>
+        <v>139928.2721946591</v>
       </c>
       <c r="AL2">
-        <v>3636818.659683228</v>
+        <v>1875736.170475752</v>
       </c>
       <c r="AM2">
-        <v>540392.1434288025</v>
+        <v>308758.9446495421</v>
       </c>
       <c r="AN2">
-        <v>714797.4414482117</v>
+        <v>307050.7836088759</v>
       </c>
       <c r="AO2">
-        <v>743725.445224762</v>
+        <v>327857.6582335688</v>
       </c>
       <c r="AP2">
-        <v>488095.1835327148</v>
+        <v>271088.4323724417</v>
       </c>
       <c r="AQ2">
-        <v>505834.4157371521</v>
+        <v>274138.5892162345</v>
       </c>
       <c r="AR2">
-        <v>364910.7671890259</v>
+        <v>214559.1721369746</v>
       </c>
       <c r="AS2">
-        <v>208797.0710945129</v>
+        <v>122207.2284201306</v>
       </c>
       <c r="AT2">
-        <v>184342.0081596375</v>
+        <v>105073.0950995565</v>
       </c>
       <c r="AU2">
-        <v>148263.9691085815</v>
+        <v>81646.23152250759</v>
       </c>
       <c r="AV2">
-        <v>121985.6654853821</v>
+        <v>77512.87986907827</v>
       </c>
       <c r="AW2">
-        <v>167027.0813369751</v>
+        <v>127537.6000545318</v>
       </c>
       <c r="AX2">
-        <v>1581840.998779297</v>
+        <v>778058.7630522089</v>
       </c>
       <c r="AY2">
-        <v>1206090.09753418</v>
+        <v>698549.108433735</v>
       </c>
       <c r="AZ2">
-        <v>1229967.673828125</v>
+        <v>584963.8875502009</v>
       </c>
       <c r="BA2">
-        <v>1664980.715576172</v>
+        <v>34075.56626506025</v>
       </c>
       <c r="BB2">
-        <v>1825044.858642578</v>
+        <v>17037.78313253012</v>
       </c>
       <c r="BC2">
-        <v>988006.9990234375</v>
+        <v>5679.261044176707</v>
       </c>
       <c r="BD2">
-        <v>295997.2412109375</v>
+        <v>704228.3694779117</v>
       </c>
       <c r="BE2">
-        <v>165788.2974853516</v>
+        <v>874606.2008032129</v>
       </c>
       <c r="BF2">
-        <v>154716.891784668</v>
+        <v>556567.5823293173</v>
       </c>
       <c r="BG2">
-        <v>312282.3854370117</v>
+        <v>5679.261044176707</v>
       </c>
       <c r="BH2">
-        <v>237086.2761230469</v>
+        <v>5679.261044176707</v>
       </c>
       <c r="BI2">
-        <v>162329.2652587891</v>
+        <v>5679.261044176707</v>
       </c>
       <c r="BJ2">
-        <v>228093.965637207</v>
+        <v>158882.6842105263</v>
       </c>
       <c r="BK2">
-        <v>205404.8770751953</v>
+        <v>88898.64473684212</v>
       </c>
       <c r="BL2">
-        <v>127129.8384399414</v>
+        <v>88898.64473684212</v>
       </c>
       <c r="BM2">
-        <v>242440.617980957</v>
+        <v>88898.64473684212</v>
       </c>
       <c r="BN2">
-        <v>218676.1038818359</v>
+        <v>47286.51315789475</v>
       </c>
       <c r="BO2">
-        <v>143326.7067871094</v>
+        <v>58635.27631578948</v>
       </c>
       <c r="BP2">
-        <v>201847.5740966797</v>
+        <v>181580.2105263158</v>
       </c>
       <c r="BQ2">
-        <v>205202.4515380859</v>
+        <v>132402.2368421053</v>
       </c>
       <c r="BR2">
-        <v>122410.6274414063</v>
+        <v>94573.0263157895</v>
       </c>
       <c r="BS2">
-        <v>203403.3797607422</v>
+        <v>96464.48684210528</v>
       </c>
       <c r="BT2">
-        <v>197437.4353027344</v>
+        <v>68092.57894736843</v>
       </c>
       <c r="BU2">
-        <v>148087.2783203125</v>
+        <v>37829.21052631579</v>
       </c>
       <c r="BV2">
-        <v>94586.75628662109</v>
+        <v>121227.512345679</v>
       </c>
       <c r="BW2">
-        <v>83840.05377197266</v>
+        <v>131237.1234567901</v>
       </c>
       <c r="BX2">
-        <v>80422.84808349609</v>
+        <v>73403.81481481482</v>
       </c>
       <c r="BY2">
-        <v>109123.5947875977</v>
+        <v>17794.86419753087</v>
       </c>
       <c r="BZ2">
-        <v>98777.91070556641</v>
+        <v>18907.04320987655</v>
       </c>
       <c r="CA2">
-        <v>57318.19427490234</v>
+        <v>14458.32716049383</v>
       </c>
       <c r="CB2">
-        <v>219448.4621582031</v>
+        <v>130124.9444444445</v>
       </c>
       <c r="CC2">
-        <v>161481.8591308594</v>
+        <v>132349.3024691358</v>
       </c>
       <c r="CD2">
-        <v>98181.12976074219</v>
+        <v>85637.78395061729</v>
       </c>
       <c r="CE2">
-        <v>213691.5545654297</v>
+        <v>20019.22222222223</v>
       </c>
       <c r="CF2">
-        <v>161983.34375</v>
+        <v>15570.50617283951</v>
       </c>
       <c r="CG2">
-        <v>58718.80346679688</v>
+        <v>20019.22222222223</v>
       </c>
       <c r="CH2">
-        <v>49093.15475463867</v>
+        <v>114195.5260115607</v>
       </c>
       <c r="CI2">
-        <v>64812.04550170898</v>
+        <v>119698.9248554913</v>
       </c>
       <c r="CJ2">
-        <v>31907.33642578125</v>
+        <v>67416.63583815029</v>
       </c>
       <c r="CK2">
-        <v>58861.26745605469</v>
+        <v>60537.387283237</v>
       </c>
       <c r="CL2">
-        <v>63582.93832397461</v>
+        <v>22013.59537572255</v>
       </c>
       <c r="CM2">
-        <v>38945.05053710938</v>
+        <v>23389.4450867052</v>
       </c>
       <c r="CN2">
-        <v>107674.2811279297</v>
+        <v>125202.323699422</v>
       </c>
       <c r="CO2">
-        <v>80396.43041992188</v>
+        <v>112819.6763005781</v>
       </c>
       <c r="CP2">
-        <v>70714.31481933594</v>
+        <v>85302.68208092486</v>
       </c>
       <c r="CQ2">
-        <v>61336.05981445313</v>
+        <v>38523.79190751445</v>
       </c>
       <c r="CR2">
-        <v>93264.3388671875</v>
+        <v>24765.29479768786</v>
       </c>
       <c r="CS2">
-        <v>42991.20861816406</v>
+        <v>27516.99421965318</v>
       </c>
       <c r="CT2">
-        <v>101726.9870605469</v>
+        <v>55627.86451612904</v>
       </c>
       <c r="CU2">
-        <v>86388.10595703125</v>
+        <v>45256.56774193549</v>
       </c>
       <c r="CV2">
-        <v>62019.84643554688</v>
+        <v>42428.03225806452</v>
       </c>
       <c r="CW2">
-        <v>100065.9138183594</v>
+        <v>12256.9870967742</v>
       </c>
       <c r="CX2">
-        <v>94595.83251953125</v>
+        <v>21685.43870967742</v>
       </c>
       <c r="CY2">
-        <v>49710.57421875</v>
+        <v>15085.52258064516</v>
       </c>
       <c r="CZ2">
-        <v>21246.86006164551</v>
+        <v>59399.24516129033</v>
       </c>
       <c r="DA2">
-        <v>17609.42001342773</v>
+        <v>57513.55483870969</v>
       </c>
       <c r="DB2">
-        <v>12388.69795227051</v>
+        <v>32056.73548387097</v>
       </c>
       <c r="DC2">
-        <v>17589.18589782715</v>
+        <v>20742.5935483871</v>
       </c>
       <c r="DD2">
-        <v>17871.60177612305</v>
+        <v>17914.05806451613</v>
       </c>
       <c r="DE2">
-        <v>12039.96208190918</v>
+        <v>13199.83225806452</v>
       </c>
       <c r="DF2">
-        <v>22352.50253295898</v>
+        <v>124408.8523489933</v>
       </c>
       <c r="DG2">
-        <v>17488.89236450195</v>
+        <v>93757.39597315437</v>
       </c>
       <c r="DH2">
-        <v>15731.14184570313</v>
+        <v>64908.96644295302</v>
       </c>
       <c r="DI2">
-        <v>18321.86178588867</v>
+        <v>86545.28859060403</v>
       </c>
       <c r="DJ2">
-        <v>25632.04370117188</v>
+        <v>46878.69798657718</v>
       </c>
       <c r="DK2">
-        <v>20326.11486816406</v>
+        <v>52287.77852348993</v>
       </c>
       <c r="DL2">
-        <v>134891.9188232422</v>
+        <v>128014.9060402685</v>
       </c>
       <c r="DM2">
-        <v>85571.55395507813</v>
+        <v>99166.47651006712</v>
       </c>
       <c r="DN2">
-        <v>89896.064453125</v>
+        <v>39666.59060402685</v>
       </c>
       <c r="DO2">
-        <v>120197.3004150391</v>
+        <v>82939.23489932886</v>
       </c>
       <c r="DP2">
-        <v>90561.16918945313</v>
+        <v>63105.93959731544</v>
       </c>
       <c r="DQ2">
-        <v>83775.67626953125</v>
+        <v>30651.45637583893</v>
       </c>
       <c r="DR2">
-        <v>58008.57006835938</v>
+        <v>29366.45161290323</v>
       </c>
       <c r="DS2">
-        <v>67865.71459960938</v>
+        <v>33104</v>
       </c>
       <c r="DT2">
-        <v>48442.22229003906</v>
+        <v>20823.48387096774</v>
       </c>
       <c r="DU2">
-        <v>62449.05023193359</v>
+        <v>11212.64516129032</v>
       </c>
       <c r="DV2">
-        <v>68919.26287841797</v>
+        <v>7475.096774193549</v>
       </c>
       <c r="DW2">
-        <v>51778.89141845703</v>
+        <v>6407.225806451614</v>
       </c>
       <c r="DX2">
-        <v>36063.50668334961</v>
+        <v>38443.35483870968</v>
       </c>
       <c r="DY2">
-        <v>13544.47515869141</v>
+        <v>36841.54838709678</v>
       </c>
       <c r="DZ2">
-        <v>19621.85452270508</v>
+        <v>23493.16129032258</v>
       </c>
       <c r="EA2">
-        <v>32323.12847900391</v>
+        <v>8542.967741935485</v>
       </c>
       <c r="EB2">
-        <v>31061.43087768555</v>
+        <v>6407.225806451614</v>
       </c>
       <c r="EC2">
-        <v>21961.15197753906</v>
+        <v>9610.83870967742</v>
       </c>
       <c r="ED2">
-        <v>90933.50512695313</v>
+        <v>40336.53846153846</v>
       </c>
       <c r="EE2">
-        <v>77707.84167480469</v>
+        <v>29580.1282051282</v>
       </c>
       <c r="EF2">
-        <v>67234.89599609375</v>
+        <v>28235.57692307692</v>
       </c>
       <c r="EG2">
-        <v>122634.1400146484</v>
+        <v>145211.5384615384</v>
       </c>
       <c r="EH2">
-        <v>106021.6932373047</v>
+        <v>60504.80769230769</v>
       </c>
       <c r="EI2">
-        <v>65136.2216796875</v>
+        <v>75294.87179487178</v>
       </c>
       <c r="EJ2">
-        <v>74867.18896484375</v>
+        <v>25546.47435897436</v>
       </c>
       <c r="EK2">
-        <v>45375.46832275391</v>
+        <v>34958.33333333333</v>
       </c>
       <c r="EL2">
-        <v>40252.46136474609</v>
+        <v>20168.26923076923</v>
       </c>
       <c r="EM2">
-        <v>59965.24536132813</v>
+        <v>141177.8846153846</v>
       </c>
       <c r="EN2">
-        <v>59814.47161865234</v>
+        <v>75294.87179487178</v>
       </c>
       <c r="EO2">
-        <v>45692.84039306641</v>
+        <v>90084.93589743589</v>
       </c>
       <c r="EP2">
-        <v>128089.1275634766</v>
+        <v>81556.17647058825</v>
       </c>
       <c r="EQ2">
-        <v>82980.58288574219</v>
+        <v>62138.03921568629</v>
       </c>
       <c r="ER2">
-        <v>57877.71496582031</v>
+        <v>45308.98692810458</v>
       </c>
       <c r="ES2">
-        <v>122418.8438110352</v>
+        <v>95796.14379084969</v>
       </c>
       <c r="ET2">
-        <v>132920.3924560547</v>
+        <v>69905.29411764706</v>
       </c>
       <c r="EU2">
-        <v>73029.34576416016</v>
+        <v>63432.58169934642</v>
       </c>
       <c r="EV2">
-        <v>69113.85424804688</v>
+        <v>72494.37908496734</v>
       </c>
       <c r="EW2">
-        <v>41847.92358398438</v>
+        <v>71199.83660130721</v>
       </c>
       <c r="EX2">
-        <v>42551.82141113281</v>
+        <v>34952.64705882354</v>
       </c>
       <c r="EY2">
-        <v>50024.99523925781</v>
+        <v>88028.88888888891</v>
       </c>
       <c r="EZ2">
-        <v>39090.13110351563</v>
+        <v>64727.12418300654</v>
       </c>
       <c r="FA2">
-        <v>31389.6845703125</v>
+        <v>31069.01960784314</v>
       </c>
       <c r="FB2">
-        <v>15172.44750976563</v>
+        <v>18117.75308641975</v>
       </c>
       <c r="FC2">
-        <v>14125.45330810547</v>
+        <v>16929.7037037037</v>
       </c>
       <c r="FD2">
-        <v>12036.01473999023</v>
+        <v>11286.46913580247</v>
       </c>
       <c r="FE2">
-        <v>22659.67776489258</v>
+        <v>24355.01234567901</v>
       </c>
       <c r="FF2">
-        <v>14115.80670166016</v>
+        <v>9801.407407407407</v>
       </c>
       <c r="FG2">
-        <v>13275.56707763672</v>
+        <v>12177.5061728395</v>
       </c>
       <c r="FH2">
-        <v>112284.6325683594</v>
+        <v>16335.67901234568</v>
       </c>
       <c r="FI2">
-        <v>66303.81600952148</v>
+        <v>16038.66666666667</v>
       </c>
       <c r="FJ2">
-        <v>36125.02462768555</v>
+        <v>12474.51851851852</v>
       </c>
       <c r="FK2">
-        <v>114339.9086303711</v>
+        <v>15147.62962962963</v>
       </c>
       <c r="FL2">
-        <v>74910.10678100586</v>
+        <v>8910.37037037037</v>
       </c>
       <c r="FM2">
-        <v>39220.35443115234</v>
+        <v>11286.46913580247</v>
       </c>
       <c r="FN2">
-        <v>59665.80322265625</v>
+        <v>15307.87037037037</v>
       </c>
       <c r="FO2">
-        <v>34585.25921630859</v>
+        <v>11706.01851851852</v>
       </c>
       <c r="FP2">
-        <v>28718.12017822266</v>
+        <v>12006.17283950617</v>
       </c>
       <c r="FQ2">
-        <v>48304.85083007813</v>
+        <v>27914.35185185185</v>
       </c>
       <c r="FR2">
-        <v>30708.27795410156</v>
+        <v>9304.783950617282</v>
       </c>
       <c r="FS2">
-        <v>33362.67895507813</v>
+        <v>12906.63580246913</v>
       </c>
       <c r="FT2">
-        <v>31848.67886352539</v>
+        <v>14107.25308641975</v>
       </c>
       <c r="FU2">
-        <v>15598.10852050781</v>
+        <v>16208.33333333333</v>
       </c>
       <c r="FV2">
-        <v>25738.58856201172</v>
+        <v>14707.56172839506</v>
       </c>
       <c r="FW2">
-        <v>19011.35064697266</v>
+        <v>18309.41358024691</v>
       </c>
       <c r="FX2">
-        <v>23070.03756713867</v>
+        <v>9004.629629629628</v>
       </c>
       <c r="FY2">
-        <v>13731.00338745117</v>
+        <v>12306.32716049383</v>
       </c>
       <c r="FZ2">
-        <v>39710.40502929688</v>
+        <v>88652.49999999999</v>
       </c>
       <c r="GA2">
-        <v>30215.19897460938</v>
+        <v>60597.91139240505</v>
       </c>
       <c r="GB2">
-        <v>18623.83312988281</v>
+        <v>56109.17721518987</v>
       </c>
       <c r="GC2">
-        <v>55850.03668212891</v>
+        <v>69575.37974683543</v>
       </c>
       <c r="GD2">
-        <v>32621.2373046875</v>
+        <v>40398.6075949367</v>
       </c>
       <c r="GE2">
-        <v>21516.65979003906</v>
+        <v>47131.70886075949</v>
       </c>
       <c r="GF2">
-        <v>11874.712890625</v>
+        <v>80797.21518987342</v>
       </c>
       <c r="GG2">
-        <v>4611.037048339844</v>
+        <v>63964.46202531645</v>
       </c>
       <c r="GH2">
-        <v>4955.318237304688</v>
+        <v>52742.62658227848</v>
       </c>
       <c r="GI2">
-        <v>11150.88557434082</v>
+        <v>58353.54430379746</v>
       </c>
       <c r="GJ2">
-        <v>4869.247940063477</v>
+        <v>38154.24050632911</v>
       </c>
       <c r="GK2">
-        <v>6084.094360351563</v>
+        <v>42642.9746835443</v>
       </c>
       <c r="GL2">
-        <v>10209.06927490234</v>
+        <v>41690.43113772455</v>
       </c>
       <c r="GM2">
-        <v>13224.45916748047</v>
+        <v>37812.25149700599</v>
       </c>
       <c r="GN2">
-        <v>7810.528930664063</v>
+        <v>31025.4371257485</v>
       </c>
       <c r="GO2">
-        <v>15005.63946533203</v>
+        <v>44599.06586826347</v>
       </c>
       <c r="GP2">
-        <v>8906.411987304688</v>
+        <v>39751.34131736527</v>
       </c>
       <c r="GQ2">
-        <v>8495.826171875</v>
+        <v>31025.4371257485</v>
       </c>
       <c r="GR2">
-        <v>67938.18908691406</v>
+        <v>44599.06586826347</v>
       </c>
       <c r="GS2">
-        <v>99308.18273925781</v>
+        <v>46538.15568862275</v>
       </c>
       <c r="GT2">
-        <v>67052.6669921875</v>
+        <v>37812.25149700599</v>
       </c>
       <c r="GU2">
-        <v>126478.8435058594</v>
+        <v>55264.05988023952</v>
       </c>
       <c r="GV2">
-        <v>106856.1428222656</v>
+        <v>31994.98203592814</v>
       </c>
       <c r="GW2">
-        <v>54258.83044433594</v>
+        <v>22299.53293413174</v>
       </c>
       <c r="GX2">
-        <v>76777.06079101563</v>
+        <v>38163.70481927711</v>
       </c>
       <c r="GY2">
-        <v>48760.30004882813</v>
+        <v>12886.44578313253</v>
       </c>
       <c r="GZ2">
-        <v>35376.77380371094</v>
+        <v>19825.30120481928</v>
       </c>
       <c r="HA2">
-        <v>76385.33642578125</v>
+        <v>53528.31325301205</v>
       </c>
       <c r="HB2">
-        <v>69053.2607421875</v>
+        <v>26268.52409638554</v>
       </c>
       <c r="HC2">
-        <v>19382.05053710938</v>
+        <v>22303.46385542169</v>
       </c>
       <c r="HD2">
-        <v>129526.9857177734</v>
+        <v>33207.37951807229</v>
       </c>
       <c r="HE2">
-        <v>121709.8986816406</v>
+        <v>28746.68674698795</v>
       </c>
       <c r="HF2">
-        <v>186158.2340087891</v>
+        <v>23294.72891566265</v>
       </c>
       <c r="HG2">
-        <v>129234.0931396484</v>
+        <v>53528.31325301205</v>
       </c>
       <c r="HH2">
-        <v>124015.5688476563</v>
+        <v>36181.17469879518</v>
       </c>
       <c r="HI2">
-        <v>111030.6588745117</v>
+        <v>17347.13855421687</v>
       </c>
       <c r="HJ2">
-        <v>28867.12405395508</v>
+        <v>61276.03125</v>
       </c>
       <c r="HK2">
-        <v>29775.14297485352</v>
+        <v>52522.3125</v>
       </c>
       <c r="HL2">
-        <v>17695.64517211914</v>
+        <v>32513.8125</v>
       </c>
       <c r="HM2">
-        <v>37565.29010009766</v>
+        <v>140059.5</v>
       </c>
       <c r="HN2">
-        <v>13952.29992675781</v>
+        <v>51271.78125</v>
       </c>
       <c r="HO2">
-        <v>18718.54119873047</v>
+        <v>67528.6875</v>
       </c>
       <c r="HP2">
-        <v>55116.46856689453</v>
+        <v>67528.6875</v>
       </c>
       <c r="HQ2">
-        <v>48918.76849365234</v>
+        <v>63777.09375</v>
       </c>
       <c r="HR2">
-        <v>30614.87390136719</v>
+        <v>40017</v>
       </c>
       <c r="HS2">
-        <v>54486.30261230469</v>
+        <v>127554.1875</v>
       </c>
       <c r="HT2">
-        <v>53749.00329589844</v>
+        <v>76282.40625</v>
       </c>
       <c r="HU2">
-        <v>35023.45141601563</v>
+        <v>51271.78125</v>
       </c>
       <c r="HV2">
-        <v>96077.06103515625</v>
+        <v>49000.61728395062</v>
       </c>
       <c r="HW2">
-        <v>34754.42724609375</v>
+        <v>27440.34567901234</v>
       </c>
       <c r="HX2">
-        <v>35441.71044921875</v>
+        <v>34300.43209876543</v>
       </c>
       <c r="HY2">
-        <v>79786.03881835938</v>
+        <v>79381</v>
       </c>
       <c r="HZ2">
-        <v>50334.37060546875</v>
+        <v>42140.53086419753</v>
       </c>
       <c r="IA2">
-        <v>50122.2333984375</v>
+        <v>52920.66666666666</v>
       </c>
       <c r="IB2">
-        <v>114290.2341308594</v>
+        <v>44100.55555555555</v>
       </c>
       <c r="IC2">
-        <v>70418.89010620117</v>
+        <v>45080.56790123456</v>
       </c>
       <c r="ID2">
-        <v>50119.97030639648</v>
+        <v>32340.40740740741</v>
       </c>
       <c r="IE2">
-        <v>118652.6946411133</v>
+        <v>73500.92592592593</v>
       </c>
       <c r="IF2">
-        <v>87664.26571655273</v>
+        <v>46060.58024691358</v>
       </c>
       <c r="IG2">
-        <v>39040.74392700195</v>
+        <v>47040.59259259259</v>
       </c>
       <c r="IH2">
-        <v>43247.57052612305</v>
+        <v>124908.1646341463</v>
       </c>
       <c r="II2">
-        <v>22222.21105957031</v>
+        <v>70893.82317073172</v>
       </c>
       <c r="IJ2">
-        <v>10129.82049560547</v>
+        <v>55139.64024390245</v>
       </c>
       <c r="IK2">
-        <v>44302.95367431641</v>
+        <v>50638.44512195123</v>
       </c>
       <c r="IL2">
-        <v>37094.28533935547</v>
+        <v>30383.06707317074</v>
       </c>
       <c r="IM2">
-        <v>21598.07336425781</v>
+        <v>33758.96341463415</v>
       </c>
       <c r="IN2">
-        <v>82398.3046875</v>
+        <v>115905.7743902439</v>
       </c>
       <c r="IO2">
-        <v>41199.15234375</v>
+        <v>115905.7743902439</v>
       </c>
       <c r="IP2">
-        <v>13733.05078125</v>
+        <v>66392.62804878049</v>
       </c>
       <c r="IQ2">
-        <v>13733.05078125</v>
+        <v>51763.74390243903</v>
       </c>
       <c r="IR2">
-        <v>27466.1015625</v>
+        <v>38260.15853658537</v>
+      </c>
+      <c r="IS2">
+        <v>22505.9756097561</v>
       </c>
       <c r="IT2">
-        <v>306739.9072265625</v>
+        <v>61122.57851239669</v>
       </c>
       <c r="IU2">
-        <v>187078.7513427734</v>
+        <v>43823.73553719008</v>
       </c>
       <c r="IV2">
-        <v>215865.4213867188</v>
+        <v>32291.17355371901</v>
       </c>
       <c r="IW2">
-        <v>304736.5280761719</v>
+        <v>53049.78512396694</v>
       </c>
       <c r="IX2">
-        <v>303990.9182128906</v>
+        <v>27678.14876033058</v>
       </c>
       <c r="IY2">
-        <v>75817.77819824219</v>
+        <v>33444.42975206611</v>
       </c>
       <c r="IZ2">
-        <v>35117.3369140625</v>
+        <v>47283.50413223141</v>
       </c>
       <c r="JA2">
-        <v>68424.78918457031</v>
+        <v>53049.78512396695</v>
       </c>
       <c r="JB2">
-        <v>75303.015625</v>
+        <v>33444.42975206612</v>
       </c>
       <c r="JC2">
-        <v>108410.1628417969</v>
+        <v>54203.04132231405</v>
       </c>
       <c r="JD2">
-        <v>44406.36315917969</v>
+        <v>36904.19834710743</v>
       </c>
       <c r="JE2">
-        <v>80743.38916015625</v>
+        <v>25371.63636363636</v>
       </c>
       <c r="JF2">
-        <v>128639.3366699219</v>
+        <v>12476.0245398773</v>
       </c>
       <c r="JG2">
-        <v>40833.04174804688</v>
+        <v>11908.93251533742</v>
       </c>
       <c r="JH2">
-        <v>57752.87255859375</v>
+        <v>11341.84049079755</v>
       </c>
       <c r="JI2">
-        <v>81184.62744140625</v>
+        <v>31190.06134969325</v>
       </c>
       <c r="JJ2">
-        <v>52685.31665039063</v>
+        <v>12476.0245398773</v>
       </c>
       <c r="JK2">
-        <v>55433.27172851563</v>
+        <v>17863.39877300613</v>
       </c>
       <c r="JL2">
-        <v>22042.56652832031</v>
+        <v>19281.12883435583</v>
       </c>
       <c r="JM2">
-        <v>37242.2890625</v>
+        <v>12759.57055214724</v>
       </c>
       <c r="JN2">
-        <v>29357.72692871094</v>
+        <v>10207.65644171779</v>
       </c>
       <c r="JO2">
-        <v>36881.72241210938</v>
+        <v>32607.79141104294</v>
       </c>
       <c r="JP2">
-        <v>35693.68688964844</v>
+        <v>16162.1226993865</v>
       </c>
       <c r="JQ2">
-        <v>27562.59326171875</v>
+        <v>15311.48466257669</v>
       </c>
       <c r="JR2">
-        <v>211202.8186035156</v>
+        <v>38316</v>
       </c>
       <c r="JS2">
-        <v>82269.64477539063</v>
+        <v>28428</v>
       </c>
       <c r="JT2">
-        <v>108157.97265625</v>
+        <v>16892</v>
       </c>
       <c r="JU2">
-        <v>184950.8747558594</v>
+        <v>46555.99999999999</v>
       </c>
       <c r="JV2">
-        <v>118223.2778320313</v>
+        <v>21012</v>
       </c>
       <c r="JW2">
-        <v>57763.26147460938</v>
+        <v>20188</v>
       </c>
       <c r="JX2">
-        <v>22636.69287109375</v>
+        <v>48615.99999999999</v>
       </c>
       <c r="JY2">
-        <v>15228.70288085938</v>
+        <v>33784</v>
       </c>
       <c r="JZ2">
-        <v>16781.24450683594</v>
+        <v>18540</v>
       </c>
       <c r="KA2">
-        <v>22369.70739746094</v>
+        <v>49027.99999999999</v>
       </c>
       <c r="KB2">
-        <v>15130.36962890625</v>
+        <v>32136</v>
       </c>
       <c r="KC2">
-        <v>23679.74377441406</v>
+        <v>21012</v>
       </c>
       <c r="KD2">
-        <v>142708.1545410156</v>
+        <v>31828.71812080537</v>
       </c>
       <c r="KE2">
-        <v>62269.82269287109</v>
+        <v>19420.91275167785</v>
       </c>
       <c r="KF2">
-        <v>69815.72332763672</v>
+        <v>16184.09395973154</v>
       </c>
       <c r="KG2">
-        <v>130675.7342529297</v>
+        <v>26973.48993288591</v>
       </c>
       <c r="KH2">
-        <v>64239.90289306641</v>
+        <v>12407.80536912752</v>
       </c>
       <c r="KI2">
-        <v>91918.73022460938</v>
+        <v>27512.95973154362</v>
       </c>
       <c r="KJ2">
-        <v>131981.6223144531</v>
+        <v>25894.55033557047</v>
       </c>
       <c r="KK2">
-        <v>78992.54370117188</v>
+        <v>16723.56375838926</v>
       </c>
       <c r="KL2">
-        <v>87985.53765869141</v>
+        <v>17263.03355704698</v>
       </c>
       <c r="KM2">
-        <v>120750.7232055664</v>
+        <v>32907.6577181208</v>
       </c>
       <c r="KN2">
-        <v>80554.12005615234</v>
+        <v>14565.68456375839</v>
       </c>
       <c r="KO2">
-        <v>37373.87463378906</v>
+        <v>30210.30872483222</v>
       </c>
       <c r="KP2">
-        <v>22191.32257080078</v>
+        <v>16413.18238993711</v>
       </c>
       <c r="KQ2">
-        <v>10818.11186218262</v>
+        <v>8719.503144654089</v>
       </c>
       <c r="KR2">
-        <v>11759.94352722168</v>
+        <v>11284.06289308176</v>
       </c>
       <c r="KS2">
-        <v>15325.076171875</v>
+        <v>67191.46540880503</v>
       </c>
       <c r="KT2">
-        <v>9240.440841674805</v>
+        <v>26158.50943396226</v>
       </c>
       <c r="KU2">
-        <v>9977.16130065918</v>
+        <v>30774.71698113207</v>
       </c>
       <c r="KV2">
-        <v>30671.77998352051</v>
+        <v>8719.503144654089</v>
       </c>
       <c r="KW2">
-        <v>9823.966674804688</v>
+        <v>9745.327044025158</v>
       </c>
       <c r="KX2">
-        <v>13257.01951599121</v>
+        <v>8206.591194968554</v>
       </c>
       <c r="KY2">
-        <v>18304.55323791504</v>
+        <v>73346.40880503145</v>
       </c>
       <c r="KZ2">
-        <v>8229.72200012207</v>
+        <v>40007.13207547169</v>
       </c>
       <c r="LA2">
-        <v>11765.76391601563</v>
+        <v>23081.03773584906</v>
       </c>
       <c r="LB2">
-        <v>168671.1983642578</v>
+        <v>15794.25641025641</v>
       </c>
       <c r="LC2">
-        <v>73344.31365966797</v>
+        <v>11098.66666666666</v>
       </c>
       <c r="LD2">
-        <v>100495.9223327637</v>
+        <v>5976.205128205127</v>
       </c>
       <c r="LE2">
-        <v>86188.21475219727</v>
+        <v>73848.82051282052</v>
       </c>
       <c r="LF2">
-        <v>75461.95959472656</v>
+        <v>28600.41025641025</v>
       </c>
       <c r="LG2">
-        <v>65962.3701171875</v>
+        <v>21770.46153846154</v>
       </c>
       <c r="LH2">
-        <v>63746.59545898438</v>
+        <v>17928.61538461538</v>
       </c>
       <c r="LI2">
-        <v>62345.56298828125</v>
+        <v>13659.89743589743</v>
       </c>
       <c r="LJ2">
-        <v>44349.14514160156</v>
+        <v>7256.820512820512</v>
       </c>
       <c r="LK2">
-        <v>76327.84631347656</v>
+        <v>72141.33333333333</v>
       </c>
       <c r="LL2">
-        <v>48280.71435546875</v>
+        <v>38845.33333333333</v>
       </c>
       <c r="LM2">
-        <v>32185.59252929688</v>
+        <v>23477.94871794872</v>
       </c>
       <c r="LN2">
-        <v>90447.21884155273</v>
+        <v>9256.000000000002</v>
       </c>
       <c r="LO2">
-        <v>50700.83627319336</v>
+        <v>3239.600000000001</v>
       </c>
       <c r="LP2">
-        <v>40359.302734375</v>
+        <v>3702.400000000001</v>
       </c>
       <c r="LQ2">
-        <v>89144.06875610352</v>
+        <v>38643.8</v>
       </c>
       <c r="LR2">
-        <v>63668.11096191406</v>
+        <v>15619.5</v>
       </c>
       <c r="LS2">
-        <v>20809.22805786133</v>
+        <v>13536.9</v>
       </c>
       <c r="LT2">
-        <v>131404.5615234375</v>
+        <v>8677.500000000002</v>
       </c>
       <c r="LU2">
-        <v>51902.80505371094</v>
+        <v>3586.700000000001</v>
       </c>
       <c r="LV2">
-        <v>64976.13647460938</v>
+        <v>4628.000000000001</v>
       </c>
       <c r="LW2">
-        <v>131347.6142578125</v>
+        <v>32280.3</v>
       </c>
       <c r="LX2">
-        <v>75118.20892333984</v>
+        <v>20941.7</v>
       </c>
       <c r="LY2">
-        <v>55840.23516845703</v>
+        <v>15850.9</v>
       </c>
       <c r="LZ2">
-        <v>119691.5768737793</v>
+        <v>10570.31055900621</v>
       </c>
       <c r="MA2">
-        <v>71161.04208374023</v>
+        <v>10570.31055900621</v>
       </c>
       <c r="MB2">
-        <v>80134.24346923828</v>
+        <v>6870.701863354038</v>
       </c>
       <c r="MC2">
-        <v>113468.7731018066</v>
+        <v>46509.36645962734</v>
       </c>
       <c r="MD2">
-        <v>69852.85079956055</v>
+        <v>19026.55900621118</v>
       </c>
       <c r="ME2">
-        <v>69676.92044067383</v>
+        <v>30653.90062111802</v>
       </c>
       <c r="MF2">
-        <v>97653.71081542969</v>
+        <v>9513.27950310559</v>
       </c>
       <c r="MG2">
-        <v>49000.76263427734</v>
+        <v>5813.670807453416</v>
       </c>
       <c r="MH2">
-        <v>74023.24713134766</v>
+        <v>7927.732919254659</v>
       </c>
       <c r="MI2">
-        <v>122756.9658813477</v>
+        <v>49151.94409937889</v>
       </c>
       <c r="MJ2">
-        <v>72532.01733398438</v>
+        <v>21140.62111801242</v>
       </c>
       <c r="MK2">
-        <v>50216.64227294922</v>
+        <v>24311.71428571429</v>
       </c>
       <c r="ML2">
-        <v>300222.1003417969</v>
+        <v>19865</v>
       </c>
       <c r="MM2">
-        <v>137818.7213134766</v>
+        <v>23975</v>
       </c>
       <c r="MN2">
-        <v>161416.0766601563</v>
+        <v>21235</v>
       </c>
       <c r="MO2">
-        <v>366688.8677978516</v>
+        <v>28769.99999999999</v>
       </c>
       <c r="MP2">
-        <v>255624.8510742188</v>
+        <v>24660</v>
       </c>
       <c r="MQ2">
-        <v>70865.78454589844</v>
+        <v>25345</v>
       </c>
       <c r="MR2">
-        <v>68064.72453308105</v>
+        <v>31510</v>
       </c>
       <c r="MS2">
-        <v>23513.56411743164</v>
+        <v>26715</v>
       </c>
       <c r="MT2">
-        <v>46703.45318603516</v>
+        <v>14385</v>
       </c>
       <c r="MU2">
-        <v>81474.15878295898</v>
+        <v>29454.99999999999</v>
       </c>
       <c r="MV2">
-        <v>31083.05360412598</v>
+        <v>22605</v>
       </c>
       <c r="MW2">
-        <v>40127.29969787598</v>
+        <v>25345</v>
       </c>
       <c r="MX2">
-        <v>118636.4149169922</v>
+        <v>70243.71428571428</v>
       </c>
       <c r="MY2">
-        <v>67088.97521972656</v>
+        <v>47847.16770186335</v>
       </c>
       <c r="MZ2">
-        <v>55742.52008056641</v>
+        <v>33594.8198757764</v>
       </c>
       <c r="NA2">
-        <v>134877.5102539063</v>
+        <v>130307.1801242236</v>
       </c>
       <c r="NB2">
-        <v>80212.17547607422</v>
+        <v>76351.86335403727</v>
       </c>
       <c r="NC2">
-        <v>64870.21813964844</v>
+        <v>57009.39130434782</v>
       </c>
       <c r="ND2">
-        <v>34437.85606384277</v>
+        <v>74315.81366459627</v>
       </c>
       <c r="NE2">
-        <v>17828.76095581055</v>
+        <v>63117.5403726708</v>
       </c>
       <c r="NF2">
-        <v>32649.70378112793</v>
+        <v>22396.54658385093</v>
       </c>
       <c r="NG2">
-        <v>39596.41110229492</v>
+        <v>94676.3105590062</v>
       </c>
       <c r="NH2">
-        <v>18784.39027404785</v>
+        <v>72279.76397515528</v>
       </c>
       <c r="NI2">
-        <v>27400.75199890137</v>
+        <v>41739.01863354037</v>
       </c>
       <c r="NJ2">
-        <v>227215.1658325195</v>
+        <v>23680.71951219512</v>
       </c>
       <c r="NK2">
-        <v>99582.70941162109</v>
+        <v>16504.74390243902</v>
       </c>
       <c r="NL2">
-        <v>91048.20825195313</v>
+        <v>18657.53658536585</v>
       </c>
       <c r="NM2">
-        <v>250002.6293334961</v>
+        <v>60278.19512195121</v>
       </c>
       <c r="NN2">
-        <v>152493.6554870605</v>
+        <v>33727.08536585366</v>
       </c>
       <c r="NO2">
-        <v>86148.87905883789</v>
+        <v>32291.89024390244</v>
       </c>
       <c r="NP2">
-        <v>128025.756149292</v>
+        <v>25833.51219512195</v>
       </c>
       <c r="NQ2">
-        <v>57157.92733764648</v>
+        <v>17939.93902439024</v>
       </c>
       <c r="NR2">
-        <v>38448.83375549316</v>
+        <v>20092.73170731707</v>
       </c>
       <c r="NS2">
-        <v>145834.3167419434</v>
+        <v>48079.03658536585</v>
       </c>
       <c r="NT2">
-        <v>86490.80360412598</v>
+        <v>34444.68292682926</v>
       </c>
       <c r="NU2">
-        <v>43703.89566040039</v>
+        <v>42338.25609756097</v>
       </c>
       <c r="NV2">
-        <v>43695.21019744873</v>
+        <v>32630.73825503356</v>
       </c>
       <c r="NW2">
-        <v>17611.10611724854</v>
+        <v>31905.61073825504</v>
       </c>
       <c r="NX2">
-        <v>15293.45672988892</v>
+        <v>16677.93288590604</v>
       </c>
       <c r="NY2">
-        <v>36876.07884216309</v>
+        <v>47858.41610738255</v>
       </c>
       <c r="NZ2">
-        <v>22450.79075241089</v>
+        <v>20303.57046979865</v>
       </c>
       <c r="OA2">
-        <v>18519.47780609131</v>
+        <v>37706.63087248322</v>
       </c>
       <c r="OB2">
-        <v>54372.17523193359</v>
+        <v>39156.88590604027</v>
       </c>
       <c r="OC2">
-        <v>22423.38107299805</v>
+        <v>14502.55033557047</v>
       </c>
       <c r="OD2">
-        <v>36006.03015136719</v>
+        <v>19578.44295302013</v>
       </c>
       <c r="OE2">
-        <v>56226.12835693359</v>
+        <v>57285.07382550335</v>
       </c>
       <c r="OF2">
-        <v>26852.82150268555</v>
+        <v>25379.46308724832</v>
       </c>
       <c r="OG2">
-        <v>28131.95074462891</v>
+        <v>39882.01342281879</v>
       </c>
       <c r="OH2">
-        <v>91675.04922485352</v>
+        <v>18126.97435897436</v>
       </c>
       <c r="OI2">
-        <v>79359.81909179688</v>
+        <v>13833.74358974359</v>
       </c>
       <c r="OJ2">
-        <v>81811.45840454102</v>
+        <v>10971.58974358974</v>
       </c>
       <c r="OK2">
-        <v>80648.53570556641</v>
+        <v>22897.23076923077</v>
       </c>
       <c r="OL2">
-        <v>67426.71569824219</v>
+        <v>17172.92307692307</v>
       </c>
       <c r="OM2">
-        <v>74373.69201660156</v>
+        <v>14310.76923076923</v>
       </c>
       <c r="ON2">
-        <v>299525.4259643555</v>
+        <v>14787.79487179487</v>
       </c>
       <c r="OO2">
-        <v>198294.5241699219</v>
+        <v>19081.02564102564</v>
       </c>
       <c r="OP2">
-        <v>128014.5081176758</v>
+        <v>11925.64102564103</v>
       </c>
       <c r="OQ2">
-        <v>234392.6777954102</v>
+        <v>19081.02564102564</v>
       </c>
       <c r="OR2">
-        <v>180255.0900878906</v>
+        <v>15264.82051282051</v>
       </c>
       <c r="OS2">
-        <v>99837.30249023438</v>
+        <v>19081.02564102564</v>
       </c>
       <c r="OT2">
-        <v>80550.1708984375</v>
+        <v>58632.72727272727</v>
       </c>
       <c r="OU2">
-        <v>42975.36016845703</v>
+        <v>21987.27272727273</v>
       </c>
       <c r="OV2">
-        <v>43291.99560546875</v>
+        <v>20521.45454545454</v>
       </c>
       <c r="OW2">
-        <v>67785.53344726563</v>
+        <v>206680.3636363636</v>
       </c>
       <c r="OX2">
-        <v>43093.79266357422</v>
+        <v>131923.6363636364</v>
       </c>
       <c r="OY2">
-        <v>56805.91082763672</v>
+        <v>105538.9090909091</v>
       </c>
       <c r="OZ2">
-        <v>114958.1827087402</v>
+        <v>48372</v>
       </c>
       <c r="PA2">
-        <v>39291.48307800293</v>
+        <v>30782.18181818182</v>
       </c>
       <c r="PB2">
-        <v>103249.352142334</v>
+        <v>30782.18181818182</v>
       </c>
       <c r="PC2">
-        <v>114118.469619751</v>
+        <v>177364</v>
       </c>
       <c r="PD2">
-        <v>47666.43705749512</v>
+        <v>134855.2727272727</v>
       </c>
       <c r="PE2">
-        <v>96458.65684509277</v>
+        <v>102607.2727272727</v>
       </c>
       <c r="PF2">
-        <v>53602.15167236328</v>
+        <v>46323.9477124183</v>
       </c>
       <c r="PG2">
-        <v>38259.27252197266</v>
+        <v>36941.88235294117</v>
       </c>
       <c r="PH2">
-        <v>37590.57293701172</v>
+        <v>23455.16339869281</v>
       </c>
       <c r="PI2">
-        <v>41205.28686523438</v>
+        <v>45737.56862745097</v>
       </c>
       <c r="PJ2">
-        <v>34706.45599365234</v>
+        <v>26387.05882352941</v>
       </c>
       <c r="PK2">
-        <v>45799.84606933594</v>
+        <v>19350.50980392157</v>
       </c>
       <c r="PL2">
-        <v>202910.0549621582</v>
+        <v>49255.84313725489</v>
       </c>
       <c r="PM2">
-        <v>104966.3740844727</v>
+        <v>40460.15686274509</v>
       </c>
       <c r="PN2">
-        <v>86868.89218139648</v>
+        <v>24041.54248366013</v>
       </c>
       <c r="PO2">
-        <v>157838.8239440918</v>
+        <v>50428.60130718954</v>
       </c>
       <c r="PP2">
-        <v>133056.0189208984</v>
+        <v>30491.71241830065</v>
       </c>
       <c r="PQ2">
-        <v>92513.38873291016</v>
+        <v>21109.64705882352</v>
       </c>
       <c r="PR2">
-        <v>179084.1236572266</v>
+        <v>29028.24427480916</v>
       </c>
       <c r="PS2">
-        <v>43513.55252075195</v>
+        <v>13194.65648854962</v>
       </c>
       <c r="PT2">
-        <v>78677.86001586914</v>
+        <v>9236.259541984733</v>
       </c>
       <c r="PU2">
-        <v>149612.2430114746</v>
+        <v>59375.95419847329</v>
       </c>
       <c r="PV2">
-        <v>128790.8619384766</v>
+        <v>22430.91603053435</v>
       </c>
       <c r="PW2">
-        <v>70198.62829589844</v>
+        <v>36945.03816793893</v>
       </c>
       <c r="PX2">
-        <v>24502.69729614258</v>
+        <v>29028.24427480916</v>
       </c>
       <c r="PY2">
-        <v>11967.04719543457</v>
+        <v>22430.91603053435</v>
       </c>
       <c r="PZ2">
-        <v>16179.07702636719</v>
+        <v>19791.98473282443</v>
       </c>
       <c r="QA2">
-        <v>23084.74444580078</v>
+        <v>48160.49618320611</v>
       </c>
       <c r="QB2">
-        <v>13248.21780395508</v>
+        <v>32326.90839694657</v>
       </c>
       <c r="QC2">
-        <v>18678.73892211914</v>
+        <v>39583.96946564886</v>
       </c>
       <c r="QD2">
-        <v>37915284.14466095</v>
+        <v>20450740.2356909</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DOMAIN|cell_var|Sum</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
           <t>#Total|cell_var|Sum</t>
         </is>
       </c>
-      <c r="B4">
-        <v>4408482.898452759</v>
-      </c>
-      <c r="C4">
-        <v>946009.4449157715</v>
-      </c>
-      <c r="D4">
-        <v>897245.6761169434</v>
-      </c>
-      <c r="E4">
-        <v>882639.2987060547</v>
-      </c>
-      <c r="F4">
-        <v>638032.8248291016</v>
-      </c>
-      <c r="G4">
-        <v>825098.6602020264</v>
-      </c>
-      <c r="H4">
-        <v>644199.4504241943</v>
-      </c>
-      <c r="I4">
-        <v>415112.5469360352</v>
-      </c>
-      <c r="J4">
-        <v>343486.3421783447</v>
-      </c>
-      <c r="K4">
-        <v>353102.7899017334</v>
-      </c>
-      <c r="L4">
-        <v>143393.4237518311</v>
-      </c>
-      <c r="M4">
-        <v>213671.2919616699</v>
-      </c>
-      <c r="N4">
-        <v>3829421.964439392</v>
-      </c>
-      <c r="O4">
-        <v>550929.4535179138</v>
-      </c>
-      <c r="P4">
-        <v>520574.638671875</v>
-      </c>
-      <c r="Q4">
-        <v>438195.7258605957</v>
-      </c>
-      <c r="R4">
-        <v>484588.8992881775</v>
-      </c>
-      <c r="S4">
-        <v>631632.0369148254</v>
-      </c>
-      <c r="T4">
-        <v>430043.5943450928</v>
-      </c>
-      <c r="U4">
-        <v>310293.7313995361</v>
-      </c>
-      <c r="V4">
-        <v>274298.5526351929</v>
-      </c>
-      <c r="W4">
-        <v>139285.0891418457</v>
-      </c>
-      <c r="X4">
-        <v>149554.7839508057</v>
-      </c>
-      <c r="Y4">
-        <v>221991.7363967896</v>
-      </c>
-      <c r="Z4">
-        <v>4525323.142944336</v>
-      </c>
-      <c r="AA4">
-        <v>1158424.232330322</v>
-      </c>
-      <c r="AB4">
-        <v>1374761.134384155</v>
-      </c>
-      <c r="AC4">
-        <v>1046085.441375732</v>
-      </c>
-      <c r="AD4">
-        <v>714990.7503967285</v>
-      </c>
-      <c r="AE4">
-        <v>796465.666595459</v>
-      </c>
-      <c r="AF4">
-        <v>576441.471786499</v>
-      </c>
-      <c r="AG4">
-        <v>428589.2324676514</v>
-      </c>
-      <c r="AH4">
-        <v>246707.7724914551</v>
-      </c>
-      <c r="AI4">
-        <v>173584.4572906494</v>
-      </c>
-      <c r="AJ4">
-        <v>159965.2857208252</v>
-      </c>
-      <c r="AK4">
-        <v>197670.8505096436</v>
-      </c>
-      <c r="AL4">
-        <v>3636818.659683228</v>
-      </c>
-      <c r="AM4">
-        <v>540392.1434288025</v>
-      </c>
-      <c r="AN4">
-        <v>714797.4414482117</v>
-      </c>
-      <c r="AO4">
-        <v>743725.445224762</v>
-      </c>
-      <c r="AP4">
-        <v>488095.1835327148</v>
-      </c>
-      <c r="AQ4">
-        <v>505834.4157371521</v>
-      </c>
-      <c r="AR4">
-        <v>364910.7671890259</v>
-      </c>
-      <c r="AS4">
-        <v>208797.0710945129</v>
-      </c>
-      <c r="AT4">
-        <v>184342.0081596375</v>
-      </c>
-      <c r="AU4">
-        <v>148263.9691085815</v>
-      </c>
-      <c r="AV4">
-        <v>121985.6654853821</v>
-      </c>
-      <c r="AW4">
-        <v>167027.0813369751</v>
-      </c>
-      <c r="AX4">
-        <v>1581840.998779297</v>
-      </c>
-      <c r="AY4">
-        <v>1206090.09753418</v>
-      </c>
-      <c r="AZ4">
-        <v>1229967.673828125</v>
-      </c>
-      <c r="BA4">
-        <v>1664980.715576172</v>
-      </c>
-      <c r="BB4">
-        <v>1825044.858642578</v>
-      </c>
-      <c r="BC4">
-        <v>988006.9990234375</v>
-      </c>
-      <c r="BD4">
-        <v>295997.2412109375</v>
-      </c>
-      <c r="BE4">
-        <v>165788.2974853516</v>
-      </c>
-      <c r="BF4">
-        <v>154716.891784668</v>
-      </c>
-      <c r="BG4">
-        <v>312282.3854370117</v>
-      </c>
-      <c r="BH4">
-        <v>237086.2761230469</v>
-      </c>
-      <c r="BI4">
-        <v>162329.2652587891</v>
-      </c>
-      <c r="BJ4">
-        <v>228093.965637207</v>
-      </c>
-      <c r="BK4">
-        <v>205404.8770751953</v>
-      </c>
-      <c r="BL4">
-        <v>127129.8384399414</v>
-      </c>
-      <c r="BM4">
-        <v>242440.617980957</v>
-      </c>
-      <c r="BN4">
-        <v>218676.1038818359</v>
-      </c>
-      <c r="BO4">
-        <v>143326.7067871094</v>
-      </c>
-      <c r="BP4">
-        <v>201847.5740966797</v>
-      </c>
-      <c r="BQ4">
-        <v>205202.4515380859</v>
-      </c>
-      <c r="BR4">
-        <v>122410.6274414063</v>
-      </c>
-      <c r="BS4">
-        <v>203403.3797607422</v>
-      </c>
-      <c r="BT4">
-        <v>197437.4353027344</v>
-      </c>
-      <c r="BU4">
-        <v>148087.2783203125</v>
-      </c>
-      <c r="BV4">
-        <v>94586.75628662109</v>
-      </c>
-      <c r="BW4">
-        <v>83840.05377197266</v>
-      </c>
-      <c r="BX4">
-        <v>80422.84808349609</v>
-      </c>
-      <c r="BY4">
-        <v>109123.5947875977</v>
-      </c>
-      <c r="BZ4">
-        <v>98777.91070556641</v>
-      </c>
-      <c r="CA4">
-        <v>57318.19427490234</v>
-      </c>
-      <c r="CB4">
-        <v>219448.4621582031</v>
-      </c>
-      <c r="CC4">
-        <v>161481.8591308594</v>
-      </c>
-      <c r="CD4">
-        <v>98181.12976074219</v>
-      </c>
-      <c r="CE4">
-        <v>213691.5545654297</v>
-      </c>
-      <c r="CF4">
-        <v>161983.34375</v>
-      </c>
-      <c r="CG4">
-        <v>58718.80346679688</v>
-      </c>
-      <c r="CH4">
-        <v>49093.15475463867</v>
-      </c>
-      <c r="CI4">
-        <v>64812.04550170898</v>
-      </c>
-      <c r="CJ4">
-        <v>31907.33642578125</v>
-      </c>
-      <c r="CK4">
-        <v>58861.26745605469</v>
-      </c>
-      <c r="CL4">
-        <v>63582.93832397461</v>
-      </c>
-      <c r="CM4">
-        <v>38945.05053710938</v>
-      </c>
-      <c r="CN4">
-        <v>107674.2811279297</v>
-      </c>
-      <c r="CO4">
-        <v>80396.43041992188</v>
-      </c>
-      <c r="CP4">
-        <v>70714.31481933594</v>
-      </c>
-      <c r="CQ4">
-        <v>61336.05981445313</v>
-      </c>
-      <c r="CR4">
-        <v>93264.3388671875</v>
-      </c>
-      <c r="CS4">
-        <v>42991.20861816406</v>
-      </c>
-      <c r="CT4">
-        <v>101726.9870605469</v>
-      </c>
-      <c r="CU4">
-        <v>86388.10595703125</v>
-      </c>
-      <c r="CV4">
-        <v>62019.84643554688</v>
-      </c>
-      <c r="CW4">
-        <v>100065.9138183594</v>
-      </c>
-      <c r="CX4">
-        <v>94595.83251953125</v>
-      </c>
-      <c r="CY4">
-        <v>49710.57421875</v>
-      </c>
-      <c r="CZ4">
-        <v>21246.86006164551</v>
-      </c>
-      <c r="DA4">
-        <v>17609.42001342773</v>
-      </c>
-      <c r="DB4">
-        <v>12388.69795227051</v>
-      </c>
-      <c r="DC4">
-        <v>17589.18589782715</v>
-      </c>
-      <c r="DD4">
-        <v>17871.60177612305</v>
-      </c>
-      <c r="DE4">
-        <v>12039.96208190918</v>
-      </c>
-      <c r="DF4">
-        <v>22352.50253295898</v>
-      </c>
-      <c r="DG4">
-        <v>17488.89236450195</v>
-      </c>
-      <c r="DH4">
-        <v>15731.14184570313</v>
-      </c>
-      <c r="DI4">
-        <v>18321.86178588867</v>
-      </c>
-      <c r="DJ4">
-        <v>25632.04370117188</v>
-      </c>
-      <c r="DK4">
-        <v>20326.11486816406</v>
-      </c>
-      <c r="DL4">
-        <v>134891.9188232422</v>
-      </c>
-      <c r="DM4">
-        <v>85571.55395507813</v>
-      </c>
-      <c r="DN4">
-        <v>89896.064453125</v>
-      </c>
-      <c r="DO4">
-        <v>120197.3004150391</v>
-      </c>
-      <c r="DP4">
-        <v>90561.16918945313</v>
-      </c>
-      <c r="DQ4">
-        <v>83775.67626953125</v>
-      </c>
-      <c r="DR4">
-        <v>58008.57006835938</v>
-      </c>
-      <c r="DS4">
-        <v>67865.71459960938</v>
-      </c>
-      <c r="DT4">
-        <v>48442.22229003906</v>
-      </c>
-      <c r="DU4">
-        <v>62449.05023193359</v>
-      </c>
-      <c r="DV4">
-        <v>68919.26287841797</v>
-      </c>
-      <c r="DW4">
-        <v>51778.89141845703</v>
-      </c>
-      <c r="DX4">
-        <v>36063.50668334961</v>
-      </c>
-      <c r="DY4">
-        <v>13544.47515869141</v>
-      </c>
-      <c r="DZ4">
-        <v>19621.85452270508</v>
-      </c>
-      <c r="EA4">
-        <v>32323.12847900391</v>
-      </c>
-      <c r="EB4">
-        <v>31061.43087768555</v>
-      </c>
-      <c r="EC4">
-        <v>21961.15197753906</v>
-      </c>
-      <c r="ED4">
-        <v>90933.50512695313</v>
-      </c>
-      <c r="EE4">
-        <v>77707.84167480469</v>
-      </c>
-      <c r="EF4">
-        <v>67234.89599609375</v>
-      </c>
-      <c r="EG4">
-        <v>122634.1400146484</v>
-      </c>
-      <c r="EH4">
-        <v>106021.6932373047</v>
-      </c>
-      <c r="EI4">
-        <v>65136.2216796875</v>
-      </c>
-      <c r="EJ4">
-        <v>74867.18896484375</v>
-      </c>
-      <c r="EK4">
-        <v>45375.46832275391</v>
-      </c>
-      <c r="EL4">
-        <v>40252.46136474609</v>
-      </c>
-      <c r="EM4">
-        <v>59965.24536132813</v>
-      </c>
-      <c r="EN4">
-        <v>59814.47161865234</v>
-      </c>
-      <c r="EO4">
-        <v>45692.84039306641</v>
-      </c>
-      <c r="EP4">
-        <v>128089.1275634766</v>
-      </c>
-      <c r="EQ4">
-        <v>82980.58288574219</v>
-      </c>
-      <c r="ER4">
-        <v>57877.71496582031</v>
-      </c>
-      <c r="ES4">
-        <v>122418.8438110352</v>
-      </c>
-      <c r="ET4">
-        <v>132920.3924560547</v>
-      </c>
-      <c r="EU4">
-        <v>73029.34576416016</v>
-      </c>
-      <c r="EV4">
-        <v>69113.85424804688</v>
-      </c>
-      <c r="EW4">
-        <v>41847.92358398438</v>
-      </c>
-      <c r="EX4">
-        <v>42551.82141113281</v>
-      </c>
-      <c r="EY4">
-        <v>50024.99523925781</v>
-      </c>
-      <c r="EZ4">
-        <v>39090.13110351563</v>
-      </c>
-      <c r="FA4">
-        <v>31389.6845703125</v>
-      </c>
-      <c r="FB4">
-        <v>15172.44750976563</v>
-      </c>
-      <c r="FC4">
-        <v>14125.45330810547</v>
-      </c>
-      <c r="FD4">
-        <v>12036.01473999023</v>
-      </c>
-      <c r="FE4">
-        <v>22659.67776489258</v>
-      </c>
-      <c r="FF4">
-        <v>14115.80670166016</v>
-      </c>
-      <c r="FG4">
-        <v>13275.56707763672</v>
-      </c>
-      <c r="FH4">
-        <v>112284.6325683594</v>
-      </c>
-      <c r="FI4">
-        <v>66303.81600952148</v>
-      </c>
-      <c r="FJ4">
-        <v>36125.02462768555</v>
-      </c>
-      <c r="FK4">
-        <v>114339.9086303711</v>
-      </c>
-      <c r="FL4">
-        <v>74910.10678100586</v>
-      </c>
-      <c r="FM4">
-        <v>39220.35443115234</v>
-      </c>
-      <c r="FN4">
-        <v>59665.80322265625</v>
-      </c>
-      <c r="FO4">
-        <v>34585.25921630859</v>
-      </c>
-      <c r="FP4">
-        <v>28718.12017822266</v>
-      </c>
-      <c r="FQ4">
-        <v>48304.85083007813</v>
-      </c>
-      <c r="FR4">
-        <v>30708.27795410156</v>
-      </c>
-      <c r="FS4">
-        <v>33362.67895507813</v>
-      </c>
-      <c r="FT4">
-        <v>31848.67886352539</v>
-      </c>
-      <c r="FU4">
-        <v>15598.10852050781</v>
-      </c>
-      <c r="FV4">
-        <v>25738.58856201172</v>
-      </c>
-      <c r="FW4">
-        <v>19011.35064697266</v>
-      </c>
-      <c r="FX4">
-        <v>23070.03756713867</v>
-      </c>
-      <c r="FY4">
-        <v>13731.00338745117</v>
-      </c>
-      <c r="FZ4">
-        <v>39710.40502929688</v>
-      </c>
-      <c r="GA4">
-        <v>30215.19897460938</v>
-      </c>
-      <c r="GB4">
-        <v>18623.83312988281</v>
-      </c>
-      <c r="GC4">
-        <v>55850.03668212891</v>
-      </c>
-      <c r="GD4">
-        <v>32621.2373046875</v>
-      </c>
-      <c r="GE4">
-        <v>21516.65979003906</v>
-      </c>
-      <c r="GF4">
-        <v>11874.712890625</v>
-      </c>
-      <c r="GG4">
-        <v>4611.037048339844</v>
-      </c>
-      <c r="GH4">
-        <v>4955.318237304688</v>
-      </c>
-      <c r="GI4">
-        <v>11150.88557434082</v>
-      </c>
-      <c r="GJ4">
-        <v>4869.247940063477</v>
-      </c>
-      <c r="GK4">
-        <v>6084.094360351563</v>
-      </c>
-      <c r="GL4">
-        <v>10209.06927490234</v>
-      </c>
-      <c r="GM4">
-        <v>13224.45916748047</v>
-      </c>
-      <c r="GN4">
-        <v>7810.528930664063</v>
-      </c>
-      <c r="GO4">
-        <v>15005.63946533203</v>
-      </c>
-      <c r="GP4">
-        <v>8906.411987304688</v>
-      </c>
-      <c r="GQ4">
-        <v>8495.826171875</v>
-      </c>
-      <c r="GR4">
-        <v>67938.18908691406</v>
-      </c>
-      <c r="GS4">
-        <v>99308.18273925781</v>
-      </c>
-      <c r="GT4">
-        <v>67052.6669921875</v>
-      </c>
-      <c r="GU4">
-        <v>126478.8435058594</v>
-      </c>
-      <c r="GV4">
-        <v>106856.1428222656</v>
-      </c>
-      <c r="GW4">
-        <v>54258.83044433594</v>
-      </c>
-      <c r="GX4">
-        <v>76777.06079101563</v>
-      </c>
-      <c r="GY4">
-        <v>48760.30004882813</v>
-      </c>
-      <c r="GZ4">
-        <v>35376.77380371094</v>
-      </c>
-      <c r="HA4">
-        <v>76385.33642578125</v>
-      </c>
-      <c r="HB4">
-        <v>69053.2607421875</v>
-      </c>
-      <c r="HC4">
-        <v>19382.05053710938</v>
-      </c>
-      <c r="HD4">
-        <v>129526.9857177734</v>
-      </c>
-      <c r="HE4">
-        <v>121709.8986816406</v>
-      </c>
-      <c r="HF4">
-        <v>186158.2340087891</v>
-      </c>
-      <c r="HG4">
-        <v>129234.0931396484</v>
-      </c>
-      <c r="HH4">
-        <v>124015.5688476563</v>
-      </c>
-      <c r="HI4">
-        <v>111030.6588745117</v>
-      </c>
-      <c r="HJ4">
-        <v>28867.12405395508</v>
-      </c>
-      <c r="HK4">
-        <v>29775.14297485352</v>
-      </c>
-      <c r="HL4">
-        <v>17695.64517211914</v>
-      </c>
-      <c r="HM4">
-        <v>37565.29010009766</v>
-      </c>
-      <c r="HN4">
-        <v>13952.29992675781</v>
-      </c>
-      <c r="HO4">
-        <v>18718.54119873047</v>
-      </c>
-      <c r="HP4">
-        <v>55116.46856689453</v>
-      </c>
-      <c r="HQ4">
-        <v>48918.76849365234</v>
-      </c>
-      <c r="HR4">
-        <v>30614.87390136719</v>
-      </c>
-      <c r="HS4">
-        <v>54486.30261230469</v>
-      </c>
-      <c r="HT4">
-        <v>53749.00329589844</v>
-      </c>
-      <c r="HU4">
-        <v>35023.45141601563</v>
-      </c>
-      <c r="HV4">
-        <v>96077.06103515625</v>
-      </c>
-      <c r="HW4">
-        <v>34754.42724609375</v>
-      </c>
-      <c r="HX4">
-        <v>35441.71044921875</v>
-      </c>
-      <c r="HY4">
-        <v>79786.03881835938</v>
-      </c>
-      <c r="HZ4">
-        <v>50334.37060546875</v>
-      </c>
-      <c r="IA4">
-        <v>50122.2333984375</v>
-      </c>
-      <c r="IB4">
-        <v>114290.2341308594</v>
-      </c>
-      <c r="IC4">
-        <v>70418.89010620117</v>
-      </c>
-      <c r="ID4">
-        <v>50119.97030639648</v>
-      </c>
-      <c r="IE4">
-        <v>118652.6946411133</v>
-      </c>
-      <c r="IF4">
-        <v>87664.26571655273</v>
-      </c>
-      <c r="IG4">
-        <v>39040.74392700195</v>
-      </c>
-      <c r="IH4">
-        <v>43247.57052612305</v>
-      </c>
-      <c r="II4">
-        <v>22222.21105957031</v>
-      </c>
-      <c r="IJ4">
-        <v>10129.82049560547</v>
-      </c>
-      <c r="IK4">
-        <v>44302.95367431641</v>
-      </c>
-      <c r="IL4">
-        <v>37094.28533935547</v>
-      </c>
-      <c r="IM4">
-        <v>21598.07336425781</v>
-      </c>
-      <c r="IN4">
-        <v>82398.3046875</v>
-      </c>
-      <c r="IO4">
-        <v>41199.15234375</v>
-      </c>
-      <c r="IP4">
-        <v>13733.05078125</v>
-      </c>
-      <c r="IQ4">
-        <v>13733.05078125</v>
-      </c>
-      <c r="IR4">
-        <v>27466.1015625</v>
-      </c>
-      <c r="IT4">
-        <v>306739.9072265625</v>
-      </c>
-      <c r="IU4">
-        <v>187078.7513427734</v>
-      </c>
-      <c r="IV4">
-        <v>215865.4213867188</v>
-      </c>
-      <c r="IW4">
-        <v>304736.5280761719</v>
-      </c>
-      <c r="IX4">
-        <v>303990.9182128906</v>
-      </c>
-      <c r="IY4">
-        <v>75817.77819824219</v>
-      </c>
-      <c r="IZ4">
-        <v>35117.3369140625</v>
-      </c>
-      <c r="JA4">
-        <v>68424.78918457031</v>
-      </c>
-      <c r="JB4">
-        <v>75303.015625</v>
-      </c>
-      <c r="JC4">
-        <v>108410.1628417969</v>
-      </c>
-      <c r="JD4">
-        <v>44406.36315917969</v>
-      </c>
-      <c r="JE4">
-        <v>80743.38916015625</v>
-      </c>
-      <c r="JF4">
-        <v>128639.3366699219</v>
-      </c>
-      <c r="JG4">
-        <v>40833.04174804688</v>
-      </c>
-      <c r="JH4">
-        <v>57752.87255859375</v>
-      </c>
-      <c r="JI4">
-        <v>81184.62744140625</v>
-      </c>
-      <c r="JJ4">
-        <v>52685.31665039063</v>
-      </c>
-      <c r="JK4">
-        <v>55433.27172851563</v>
-      </c>
-      <c r="JL4">
-        <v>22042.56652832031</v>
-      </c>
-      <c r="JM4">
-        <v>37242.2890625</v>
-      </c>
-      <c r="JN4">
-        <v>29357.72692871094</v>
-      </c>
-      <c r="JO4">
-        <v>36881.72241210938</v>
-      </c>
-      <c r="JP4">
-        <v>35693.68688964844</v>
-      </c>
-      <c r="JQ4">
-        <v>27562.59326171875</v>
-      </c>
-      <c r="JR4">
-        <v>211202.8186035156</v>
-      </c>
-      <c r="JS4">
-        <v>82269.64477539063</v>
-      </c>
-      <c r="JT4">
-        <v>108157.97265625</v>
-      </c>
-      <c r="JU4">
-        <v>184950.8747558594</v>
-      </c>
-      <c r="JV4">
-        <v>118223.2778320313</v>
-      </c>
-      <c r="JW4">
-        <v>57763.26147460938</v>
-      </c>
-      <c r="JX4">
-        <v>22636.69287109375</v>
-      </c>
-      <c r="JY4">
-        <v>15228.70288085938</v>
-      </c>
-      <c r="JZ4">
-        <v>16781.24450683594</v>
-      </c>
-      <c r="KA4">
-        <v>22369.70739746094</v>
-      </c>
-      <c r="KB4">
-        <v>15130.36962890625</v>
-      </c>
-      <c r="KC4">
-        <v>23679.74377441406</v>
-      </c>
-      <c r="KD4">
-        <v>142708.1545410156</v>
-      </c>
-      <c r="KE4">
-        <v>62269.82269287109</v>
-      </c>
-      <c r="KF4">
-        <v>69815.72332763672</v>
-      </c>
-      <c r="KG4">
-        <v>130675.7342529297</v>
-      </c>
-      <c r="KH4">
-        <v>64239.90289306641</v>
-      </c>
-      <c r="KI4">
-        <v>91918.73022460938</v>
-      </c>
-      <c r="KJ4">
-        <v>131981.6223144531</v>
-      </c>
-      <c r="KK4">
-        <v>78992.54370117188</v>
-      </c>
-      <c r="KL4">
-        <v>87985.53765869141</v>
-      </c>
-      <c r="KM4">
-        <v>120750.7232055664</v>
-      </c>
-      <c r="KN4">
-        <v>80554.12005615234</v>
-      </c>
-      <c r="KO4">
-        <v>37373.87463378906</v>
-      </c>
-      <c r="KP4">
-        <v>22191.32257080078</v>
-      </c>
-      <c r="KQ4">
-        <v>10818.11186218262</v>
-      </c>
-      <c r="KR4">
-        <v>11759.94352722168</v>
-      </c>
-      <c r="KS4">
-        <v>15325.076171875</v>
-      </c>
-      <c r="KT4">
-        <v>9240.440841674805</v>
-      </c>
-      <c r="KU4">
-        <v>9977.16130065918</v>
-      </c>
-      <c r="KV4">
-        <v>30671.77998352051</v>
-      </c>
-      <c r="KW4">
-        <v>9823.966674804688</v>
-      </c>
-      <c r="KX4">
-        <v>13257.01951599121</v>
-      </c>
-      <c r="KY4">
-        <v>18304.55323791504</v>
-      </c>
-      <c r="KZ4">
-        <v>8229.72200012207</v>
-      </c>
-      <c r="LA4">
-        <v>11765.76391601563</v>
-      </c>
-      <c r="LB4">
-        <v>168671.1983642578</v>
-      </c>
-      <c r="LC4">
-        <v>73344.31365966797</v>
-      </c>
-      <c r="LD4">
-        <v>100495.9223327637</v>
-      </c>
-      <c r="LE4">
-        <v>86188.21475219727</v>
-      </c>
-      <c r="LF4">
-        <v>75461.95959472656</v>
-      </c>
-      <c r="LG4">
-        <v>65962.3701171875</v>
-      </c>
-      <c r="LH4">
-        <v>63746.59545898438</v>
-      </c>
-      <c r="LI4">
-        <v>62345.56298828125</v>
-      </c>
-      <c r="LJ4">
-        <v>44349.14514160156</v>
-      </c>
-      <c r="LK4">
-        <v>76327.84631347656</v>
-      </c>
-      <c r="LL4">
-        <v>48280.71435546875</v>
-      </c>
-      <c r="LM4">
-        <v>32185.59252929688</v>
-      </c>
-      <c r="LN4">
-        <v>90447.21884155273</v>
-      </c>
-      <c r="LO4">
-        <v>50700.83627319336</v>
-      </c>
-      <c r="LP4">
-        <v>40359.302734375</v>
-      </c>
-      <c r="LQ4">
-        <v>89144.06875610352</v>
-      </c>
-      <c r="LR4">
-        <v>63668.11096191406</v>
-      </c>
-      <c r="LS4">
-        <v>20809.22805786133</v>
-      </c>
-      <c r="LT4">
-        <v>131404.5615234375</v>
-      </c>
-      <c r="LU4">
-        <v>51902.80505371094</v>
-      </c>
-      <c r="LV4">
-        <v>64976.13647460938</v>
-      </c>
-      <c r="LW4">
-        <v>131347.6142578125</v>
-      </c>
-      <c r="LX4">
-        <v>75118.20892333984</v>
-      </c>
-      <c r="LY4">
-        <v>55840.23516845703</v>
-      </c>
-      <c r="LZ4">
-        <v>119691.5768737793</v>
-      </c>
-      <c r="MA4">
-        <v>71161.04208374023</v>
-      </c>
-      <c r="MB4">
-        <v>80134.24346923828</v>
-      </c>
-      <c r="MC4">
-        <v>113468.7731018066</v>
-      </c>
-      <c r="MD4">
-        <v>69852.85079956055</v>
-      </c>
-      <c r="ME4">
-        <v>69676.92044067383</v>
-      </c>
-      <c r="MF4">
-        <v>97653.71081542969</v>
-      </c>
-      <c r="MG4">
-        <v>49000.76263427734</v>
-      </c>
-      <c r="MH4">
-        <v>74023.24713134766</v>
-      </c>
-      <c r="MI4">
-        <v>122756.9658813477</v>
-      </c>
-      <c r="MJ4">
-        <v>72532.01733398438</v>
-      </c>
-      <c r="MK4">
-        <v>50216.64227294922</v>
-      </c>
-      <c r="ML4">
-        <v>300222.1003417969</v>
-      </c>
-      <c r="MM4">
-        <v>137818.7213134766</v>
-      </c>
-      <c r="MN4">
-        <v>161416.0766601563</v>
-      </c>
-      <c r="MO4">
-        <v>366688.8677978516</v>
-      </c>
-      <c r="MP4">
-        <v>255624.8510742188</v>
-      </c>
-      <c r="MQ4">
-        <v>70865.78454589844</v>
-      </c>
-      <c r="MR4">
-        <v>68064.72453308105</v>
-      </c>
-      <c r="MS4">
-        <v>23513.56411743164</v>
-      </c>
-      <c r="MT4">
-        <v>46703.45318603516</v>
-      </c>
-      <c r="MU4">
-        <v>81474.15878295898</v>
-      </c>
-      <c r="MV4">
-        <v>31083.05360412598</v>
-      </c>
-      <c r="MW4">
-        <v>40127.29969787598</v>
-      </c>
-      <c r="MX4">
-        <v>118636.4149169922</v>
-      </c>
-      <c r="MY4">
-        <v>67088.97521972656</v>
-      </c>
-      <c r="MZ4">
-        <v>55742.52008056641</v>
-      </c>
-      <c r="NA4">
-        <v>134877.5102539063</v>
-      </c>
-      <c r="NB4">
-        <v>80212.17547607422</v>
-      </c>
-      <c r="NC4">
-        <v>64870.21813964844</v>
-      </c>
-      <c r="ND4">
-        <v>34437.85606384277</v>
-      </c>
-      <c r="NE4">
-        <v>17828.76095581055</v>
-      </c>
-      <c r="NF4">
-        <v>32649.70378112793</v>
-      </c>
-      <c r="NG4">
-        <v>39596.41110229492</v>
-      </c>
-      <c r="NH4">
-        <v>18784.39027404785</v>
-      </c>
-      <c r="NI4">
-        <v>27400.75199890137</v>
-      </c>
-      <c r="NJ4">
-        <v>227215.1658325195</v>
-      </c>
-      <c r="NK4">
-        <v>99582.70941162109</v>
-      </c>
-      <c r="NL4">
-        <v>91048.20825195313</v>
-      </c>
-      <c r="NM4">
-        <v>250002.6293334961</v>
-      </c>
-      <c r="NN4">
-        <v>152493.6554870605</v>
-      </c>
-      <c r="NO4">
-        <v>86148.87905883789</v>
-      </c>
-      <c r="NP4">
-        <v>128025.756149292</v>
-      </c>
-      <c r="NQ4">
-        <v>57157.92733764648</v>
-      </c>
-      <c r="NR4">
-        <v>38448.83375549316</v>
-      </c>
-      <c r="NS4">
-        <v>145834.3167419434</v>
-      </c>
-      <c r="NT4">
-        <v>86490.80360412598</v>
-      </c>
-      <c r="NU4">
-        <v>43703.89566040039</v>
-      </c>
-      <c r="NV4">
-        <v>43695.21019744873</v>
-      </c>
-      <c r="NW4">
-        <v>17611.10611724854</v>
-      </c>
-      <c r="NX4">
-        <v>15293.45672988892</v>
-      </c>
-      <c r="NY4">
-        <v>36876.07884216309</v>
-      </c>
-      <c r="NZ4">
-        <v>22450.79075241089</v>
-      </c>
-      <c r="OA4">
-        <v>18519.47780609131</v>
-      </c>
-      <c r="OB4">
-        <v>54372.17523193359</v>
-      </c>
-      <c r="OC4">
-        <v>22423.38107299805</v>
-      </c>
-      <c r="OD4">
-        <v>36006.03015136719</v>
-      </c>
-      <c r="OE4">
-        <v>56226.12835693359</v>
-      </c>
-      <c r="OF4">
-        <v>26852.82150268555</v>
-      </c>
-      <c r="OG4">
-        <v>28131.95074462891</v>
-      </c>
-      <c r="OH4">
-        <v>91675.04922485352</v>
-      </c>
-      <c r="OI4">
-        <v>79359.81909179688</v>
-      </c>
-      <c r="OJ4">
-        <v>81811.45840454102</v>
-      </c>
-      <c r="OK4">
-        <v>80648.53570556641</v>
-      </c>
-      <c r="OL4">
-        <v>67426.71569824219</v>
-      </c>
-      <c r="OM4">
-        <v>74373.69201660156</v>
-      </c>
-      <c r="ON4">
-        <v>299525.4259643555</v>
-      </c>
-      <c r="OO4">
-        <v>198294.5241699219</v>
-      </c>
-      <c r="OP4">
-        <v>128014.5081176758</v>
-      </c>
-      <c r="OQ4">
-        <v>234392.6777954102</v>
-      </c>
-      <c r="OR4">
-        <v>180255.0900878906</v>
-      </c>
-      <c r="OS4">
-        <v>99837.30249023438</v>
-      </c>
-      <c r="OT4">
-        <v>80550.1708984375</v>
-      </c>
-      <c r="OU4">
-        <v>42975.36016845703</v>
-      </c>
-      <c r="OV4">
-        <v>43291.99560546875</v>
-      </c>
-      <c r="OW4">
-        <v>67785.53344726563</v>
-      </c>
-      <c r="OX4">
-        <v>43093.79266357422</v>
-      </c>
-      <c r="OY4">
-        <v>56805.91082763672</v>
-      </c>
-      <c r="OZ4">
-        <v>114958.1827087402</v>
-      </c>
-      <c r="PA4">
-        <v>39291.48307800293</v>
-      </c>
-      <c r="PB4">
-        <v>103249.352142334</v>
-      </c>
-      <c r="PC4">
-        <v>114118.469619751</v>
-      </c>
-      <c r="PD4">
-        <v>47666.43705749512</v>
-      </c>
-      <c r="PE4">
-        <v>96458.65684509277</v>
-      </c>
-      <c r="PF4">
-        <v>53602.15167236328</v>
-      </c>
-      <c r="PG4">
-        <v>38259.27252197266</v>
-      </c>
-      <c r="PH4">
-        <v>37590.57293701172</v>
-      </c>
-      <c r="PI4">
-        <v>41205.28686523438</v>
-      </c>
-      <c r="PJ4">
-        <v>34706.45599365234</v>
-      </c>
-      <c r="PK4">
-        <v>45799.84606933594</v>
-      </c>
-      <c r="PL4">
-        <v>202910.0549621582</v>
-      </c>
-      <c r="PM4">
-        <v>104966.3740844727</v>
-      </c>
-      <c r="PN4">
-        <v>86868.89218139648</v>
-      </c>
-      <c r="PO4">
-        <v>157838.8239440918</v>
-      </c>
-      <c r="PP4">
-        <v>133056.0189208984</v>
-      </c>
-      <c r="PQ4">
-        <v>92513.38873291016</v>
-      </c>
-      <c r="PR4">
-        <v>179084.1236572266</v>
-      </c>
-      <c r="PS4">
-        <v>43513.55252075195</v>
-      </c>
-      <c r="PT4">
-        <v>78677.86001586914</v>
-      </c>
-      <c r="PU4">
-        <v>149612.2430114746</v>
-      </c>
-      <c r="PV4">
-        <v>128790.8619384766</v>
-      </c>
-      <c r="PW4">
-        <v>70198.62829589844</v>
-      </c>
-      <c r="PX4">
-        <v>24502.69729614258</v>
-      </c>
-      <c r="PY4">
-        <v>11967.04719543457</v>
-      </c>
-      <c r="PZ4">
-        <v>16179.07702636719</v>
-      </c>
-      <c r="QA4">
-        <v>23084.74444580078</v>
-      </c>
-      <c r="QB4">
-        <v>13248.21780395508</v>
-      </c>
-      <c r="QC4">
-        <v>18678.73892211914</v>
-      </c>
-      <c r="QD4">
-        <v>37915284.14466095</v>
+      <c r="B3">
+        <v>2435086.577816167</v>
+      </c>
+      <c r="C3">
+        <v>617097.8219488491</v>
+      </c>
+      <c r="D3">
+        <v>553058.3261356597</v>
+      </c>
+      <c r="E3">
+        <v>417616.0721064299</v>
+      </c>
+      <c r="F3">
+        <v>348636.2633479309</v>
+      </c>
+      <c r="G3">
+        <v>369271.1880225898</v>
+      </c>
+      <c r="H3">
+        <v>372976.6165509298</v>
+      </c>
+      <c r="I3">
+        <v>245730.2234402738</v>
+      </c>
+      <c r="J3">
+        <v>181342.2359124488</v>
+      </c>
+      <c r="K3">
+        <v>142837.4718534084</v>
+      </c>
+      <c r="L3">
+        <v>92009.33744812843</v>
+      </c>
+      <c r="M3">
+        <v>123319.6329647891</v>
+      </c>
+      <c r="N3">
+        <v>2028247.831144195</v>
+      </c>
+      <c r="O3">
+        <v>289113.8729801912</v>
+      </c>
+      <c r="P3">
+        <v>304186.9462738459</v>
+      </c>
+      <c r="Q3">
+        <v>249148.3050379899</v>
+      </c>
+      <c r="R3">
+        <v>234501.2002687122</v>
+      </c>
+      <c r="S3">
+        <v>271550.5505709473</v>
+      </c>
+      <c r="T3">
+        <v>232246.34146675</v>
+      </c>
+      <c r="U3">
+        <v>186151.7943184116</v>
+      </c>
+      <c r="V3">
+        <v>138351.6975941383</v>
+      </c>
+      <c r="W3">
+        <v>88947.0143559572</v>
+      </c>
+      <c r="X3">
+        <v>93444.74756504585</v>
+      </c>
+      <c r="Y3">
+        <v>107974.1196508589</v>
+      </c>
+      <c r="Z3">
+        <v>2379789.993137228</v>
+      </c>
+      <c r="AA3">
+        <v>713605.3510025752</v>
+      </c>
+      <c r="AB3">
+        <v>714320.2934210722</v>
+      </c>
+      <c r="AC3">
+        <v>474842.2164412421</v>
+      </c>
+      <c r="AD3">
+        <v>429500.8705300601</v>
+      </c>
+      <c r="AE3">
+        <v>436193.2225619344</v>
+      </c>
+      <c r="AF3">
+        <v>326884.009823251</v>
+      </c>
+      <c r="AG3">
+        <v>247075.4326166104</v>
+      </c>
+      <c r="AH3">
+        <v>157783.0028769656</v>
+      </c>
+      <c r="AI3">
+        <v>117515.0096540628</v>
+      </c>
+      <c r="AJ3">
+        <v>97289.58699739751</v>
+      </c>
+      <c r="AK3">
+        <v>139928.2721946591</v>
+      </c>
+      <c r="AL3">
+        <v>1875736.170475752</v>
+      </c>
+      <c r="AM3">
+        <v>308758.9446495421</v>
+      </c>
+      <c r="AN3">
+        <v>307050.7836088759</v>
+      </c>
+      <c r="AO3">
+        <v>327857.6582335688</v>
+      </c>
+      <c r="AP3">
+        <v>271088.4323724417</v>
+      </c>
+      <c r="AQ3">
+        <v>274138.5892162345</v>
+      </c>
+      <c r="AR3">
+        <v>214559.1721369746</v>
+      </c>
+      <c r="AS3">
+        <v>122207.2284201306</v>
+      </c>
+      <c r="AT3">
+        <v>105073.0950995565</v>
+      </c>
+      <c r="AU3">
+        <v>81646.23152250759</v>
+      </c>
+      <c r="AV3">
+        <v>77512.87986907827</v>
+      </c>
+      <c r="AW3">
+        <v>127537.6000545318</v>
+      </c>
+      <c r="AX3">
+        <v>778058.7630522089</v>
+      </c>
+      <c r="AY3">
+        <v>698549.108433735</v>
+      </c>
+      <c r="AZ3">
+        <v>584963.8875502009</v>
+      </c>
+      <c r="BA3">
+        <v>34075.56626506025</v>
+      </c>
+      <c r="BB3">
+        <v>17037.78313253012</v>
+      </c>
+      <c r="BC3">
+        <v>5679.261044176707</v>
+      </c>
+      <c r="BD3">
+        <v>704228.3694779117</v>
+      </c>
+      <c r="BE3">
+        <v>874606.2008032129</v>
+      </c>
+      <c r="BF3">
+        <v>556567.5823293173</v>
+      </c>
+      <c r="BG3">
+        <v>5679.261044176707</v>
+      </c>
+      <c r="BH3">
+        <v>5679.261044176707</v>
+      </c>
+      <c r="BI3">
+        <v>5679.261044176707</v>
+      </c>
+      <c r="BJ3">
+        <v>158882.6842105263</v>
+      </c>
+      <c r="BK3">
+        <v>88898.64473684212</v>
+      </c>
+      <c r="BL3">
+        <v>88898.64473684212</v>
+      </c>
+      <c r="BM3">
+        <v>88898.64473684212</v>
+      </c>
+      <c r="BN3">
+        <v>47286.51315789475</v>
+      </c>
+      <c r="BO3">
+        <v>58635.27631578948</v>
+      </c>
+      <c r="BP3">
+        <v>181580.2105263158</v>
+      </c>
+      <c r="BQ3">
+        <v>132402.2368421053</v>
+      </c>
+      <c r="BR3">
+        <v>94573.0263157895</v>
+      </c>
+      <c r="BS3">
+        <v>96464.48684210528</v>
+      </c>
+      <c r="BT3">
+        <v>68092.57894736843</v>
+      </c>
+      <c r="BU3">
+        <v>37829.21052631579</v>
+      </c>
+      <c r="BV3">
+        <v>121227.512345679</v>
+      </c>
+      <c r="BW3">
+        <v>131237.1234567901</v>
+      </c>
+      <c r="BX3">
+        <v>73403.81481481482</v>
+      </c>
+      <c r="BY3">
+        <v>17794.86419753087</v>
+      </c>
+      <c r="BZ3">
+        <v>18907.04320987655</v>
+      </c>
+      <c r="CA3">
+        <v>14458.32716049383</v>
+      </c>
+      <c r="CB3">
+        <v>130124.9444444445</v>
+      </c>
+      <c r="CC3">
+        <v>132349.3024691358</v>
+      </c>
+      <c r="CD3">
+        <v>85637.78395061729</v>
+      </c>
+      <c r="CE3">
+        <v>20019.22222222223</v>
+      </c>
+      <c r="CF3">
+        <v>15570.50617283951</v>
+      </c>
+      <c r="CG3">
+        <v>20019.22222222223</v>
+      </c>
+      <c r="CH3">
+        <v>114195.5260115607</v>
+      </c>
+      <c r="CI3">
+        <v>119698.9248554913</v>
+      </c>
+      <c r="CJ3">
+        <v>67416.63583815029</v>
+      </c>
+      <c r="CK3">
+        <v>60537.387283237</v>
+      </c>
+      <c r="CL3">
+        <v>22013.59537572255</v>
+      </c>
+      <c r="CM3">
+        <v>23389.4450867052</v>
+      </c>
+      <c r="CN3">
+        <v>125202.323699422</v>
+      </c>
+      <c r="CO3">
+        <v>112819.6763005781</v>
+      </c>
+      <c r="CP3">
+        <v>85302.68208092486</v>
+      </c>
+      <c r="CQ3">
+        <v>38523.79190751445</v>
+      </c>
+      <c r="CR3">
+        <v>24765.29479768786</v>
+      </c>
+      <c r="CS3">
+        <v>27516.99421965318</v>
+      </c>
+      <c r="CT3">
+        <v>55627.86451612904</v>
+      </c>
+      <c r="CU3">
+        <v>45256.56774193549</v>
+      </c>
+      <c r="CV3">
+        <v>42428.03225806452</v>
+      </c>
+      <c r="CW3">
+        <v>12256.9870967742</v>
+      </c>
+      <c r="CX3">
+        <v>21685.43870967742</v>
+      </c>
+      <c r="CY3">
+        <v>15085.52258064516</v>
+      </c>
+      <c r="CZ3">
+        <v>59399.24516129033</v>
+      </c>
+      <c r="DA3">
+        <v>57513.55483870969</v>
+      </c>
+      <c r="DB3">
+        <v>32056.73548387097</v>
+      </c>
+      <c r="DC3">
+        <v>20742.5935483871</v>
+      </c>
+      <c r="DD3">
+        <v>17914.05806451613</v>
+      </c>
+      <c r="DE3">
+        <v>13199.83225806452</v>
+      </c>
+      <c r="DF3">
+        <v>124408.8523489933</v>
+      </c>
+      <c r="DG3">
+        <v>93757.39597315437</v>
+      </c>
+      <c r="DH3">
+        <v>64908.96644295302</v>
+      </c>
+      <c r="DI3">
+        <v>86545.28859060403</v>
+      </c>
+      <c r="DJ3">
+        <v>46878.69798657718</v>
+      </c>
+      <c r="DK3">
+        <v>52287.77852348993</v>
+      </c>
+      <c r="DL3">
+        <v>128014.9060402685</v>
+      </c>
+      <c r="DM3">
+        <v>99166.47651006712</v>
+      </c>
+      <c r="DN3">
+        <v>39666.59060402685</v>
+      </c>
+      <c r="DO3">
+        <v>82939.23489932886</v>
+      </c>
+      <c r="DP3">
+        <v>63105.93959731544</v>
+      </c>
+      <c r="DQ3">
+        <v>30651.45637583893</v>
+      </c>
+      <c r="DR3">
+        <v>29366.45161290323</v>
+      </c>
+      <c r="DS3">
+        <v>33104</v>
+      </c>
+      <c r="DT3">
+        <v>20823.48387096774</v>
+      </c>
+      <c r="DU3">
+        <v>11212.64516129032</v>
+      </c>
+      <c r="DV3">
+        <v>7475.096774193549</v>
+      </c>
+      <c r="DW3">
+        <v>6407.225806451614</v>
+      </c>
+      <c r="DX3">
+        <v>38443.35483870968</v>
+      </c>
+      <c r="DY3">
+        <v>36841.54838709678</v>
+      </c>
+      <c r="DZ3">
+        <v>23493.16129032258</v>
+      </c>
+      <c r="EA3">
+        <v>8542.967741935485</v>
+      </c>
+      <c r="EB3">
+        <v>6407.225806451614</v>
+      </c>
+      <c r="EC3">
+        <v>9610.83870967742</v>
+      </c>
+      <c r="ED3">
+        <v>40336.53846153846</v>
+      </c>
+      <c r="EE3">
+        <v>29580.1282051282</v>
+      </c>
+      <c r="EF3">
+        <v>28235.57692307692</v>
+      </c>
+      <c r="EG3">
+        <v>145211.5384615384</v>
+      </c>
+      <c r="EH3">
+        <v>60504.80769230769</v>
+      </c>
+      <c r="EI3">
+        <v>75294.87179487178</v>
+      </c>
+      <c r="EJ3">
+        <v>25546.47435897436</v>
+      </c>
+      <c r="EK3">
+        <v>34958.33333333333</v>
+      </c>
+      <c r="EL3">
+        <v>20168.26923076923</v>
+      </c>
+      <c r="EM3">
+        <v>141177.8846153846</v>
+      </c>
+      <c r="EN3">
+        <v>75294.87179487178</v>
+      </c>
+      <c r="EO3">
+        <v>90084.93589743589</v>
+      </c>
+      <c r="EP3">
+        <v>81556.17647058825</v>
+      </c>
+      <c r="EQ3">
+        <v>62138.03921568629</v>
+      </c>
+      <c r="ER3">
+        <v>45308.98692810458</v>
+      </c>
+      <c r="ES3">
+        <v>95796.14379084969</v>
+      </c>
+      <c r="ET3">
+        <v>69905.29411764706</v>
+      </c>
+      <c r="EU3">
+        <v>63432.58169934642</v>
+      </c>
+      <c r="EV3">
+        <v>72494.37908496734</v>
+      </c>
+      <c r="EW3">
+        <v>71199.83660130721</v>
+      </c>
+      <c r="EX3">
+        <v>34952.64705882354</v>
+      </c>
+      <c r="EY3">
+        <v>88028.88888888891</v>
+      </c>
+      <c r="EZ3">
+        <v>64727.12418300654</v>
+      </c>
+      <c r="FA3">
+        <v>31069.01960784314</v>
+      </c>
+      <c r="FB3">
+        <v>18117.75308641975</v>
+      </c>
+      <c r="FC3">
+        <v>16929.7037037037</v>
+      </c>
+      <c r="FD3">
+        <v>11286.46913580247</v>
+      </c>
+      <c r="FE3">
+        <v>24355.01234567901</v>
+      </c>
+      <c r="FF3">
+        <v>9801.407407407407</v>
+      </c>
+      <c r="FG3">
+        <v>12177.5061728395</v>
+      </c>
+      <c r="FH3">
+        <v>16335.67901234568</v>
+      </c>
+      <c r="FI3">
+        <v>16038.66666666667</v>
+      </c>
+      <c r="FJ3">
+        <v>12474.51851851852</v>
+      </c>
+      <c r="FK3">
+        <v>15147.62962962963</v>
+      </c>
+      <c r="FL3">
+        <v>8910.37037037037</v>
+      </c>
+      <c r="FM3">
+        <v>11286.46913580247</v>
+      </c>
+      <c r="FN3">
+        <v>15307.87037037037</v>
+      </c>
+      <c r="FO3">
+        <v>11706.01851851852</v>
+      </c>
+      <c r="FP3">
+        <v>12006.17283950617</v>
+      </c>
+      <c r="FQ3">
+        <v>27914.35185185185</v>
+      </c>
+      <c r="FR3">
+        <v>9304.783950617282</v>
+      </c>
+      <c r="FS3">
+        <v>12906.63580246913</v>
+      </c>
+      <c r="FT3">
+        <v>14107.25308641975</v>
+      </c>
+      <c r="FU3">
+        <v>16208.33333333333</v>
+      </c>
+      <c r="FV3">
+        <v>14707.56172839506</v>
+      </c>
+      <c r="FW3">
+        <v>18309.41358024691</v>
+      </c>
+      <c r="FX3">
+        <v>9004.629629629628</v>
+      </c>
+      <c r="FY3">
+        <v>12306.32716049383</v>
+      </c>
+      <c r="FZ3">
+        <v>88652.49999999999</v>
+      </c>
+      <c r="GA3">
+        <v>60597.91139240505</v>
+      </c>
+      <c r="GB3">
+        <v>56109.17721518987</v>
+      </c>
+      <c r="GC3">
+        <v>69575.37974683543</v>
+      </c>
+      <c r="GD3">
+        <v>40398.6075949367</v>
+      </c>
+      <c r="GE3">
+        <v>47131.70886075949</v>
+      </c>
+      <c r="GF3">
+        <v>80797.21518987342</v>
+      </c>
+      <c r="GG3">
+        <v>63964.46202531645</v>
+      </c>
+      <c r="GH3">
+        <v>52742.62658227848</v>
+      </c>
+      <c r="GI3">
+        <v>58353.54430379746</v>
+      </c>
+      <c r="GJ3">
+        <v>38154.24050632911</v>
+      </c>
+      <c r="GK3">
+        <v>42642.9746835443</v>
+      </c>
+      <c r="GL3">
+        <v>41690.43113772455</v>
+      </c>
+      <c r="GM3">
+        <v>37812.25149700599</v>
+      </c>
+      <c r="GN3">
+        <v>31025.4371257485</v>
+      </c>
+      <c r="GO3">
+        <v>44599.06586826347</v>
+      </c>
+      <c r="GP3">
+        <v>39751.34131736527</v>
+      </c>
+      <c r="GQ3">
+        <v>31025.4371257485</v>
+      </c>
+      <c r="GR3">
+        <v>44599.06586826347</v>
+      </c>
+      <c r="GS3">
+        <v>46538.15568862275</v>
+      </c>
+      <c r="GT3">
+        <v>37812.25149700599</v>
+      </c>
+      <c r="GU3">
+        <v>55264.05988023952</v>
+      </c>
+      <c r="GV3">
+        <v>31994.98203592814</v>
+      </c>
+      <c r="GW3">
+        <v>22299.53293413174</v>
+      </c>
+      <c r="GX3">
+        <v>38163.70481927711</v>
+      </c>
+      <c r="GY3">
+        <v>12886.44578313253</v>
+      </c>
+      <c r="GZ3">
+        <v>19825.30120481928</v>
+      </c>
+      <c r="HA3">
+        <v>53528.31325301205</v>
+      </c>
+      <c r="HB3">
+        <v>26268.52409638554</v>
+      </c>
+      <c r="HC3">
+        <v>22303.46385542169</v>
+      </c>
+      <c r="HD3">
+        <v>33207.37951807229</v>
+      </c>
+      <c r="HE3">
+        <v>28746.68674698795</v>
+      </c>
+      <c r="HF3">
+        <v>23294.72891566265</v>
+      </c>
+      <c r="HG3">
+        <v>53528.31325301205</v>
+      </c>
+      <c r="HH3">
+        <v>36181.17469879518</v>
+      </c>
+      <c r="HI3">
+        <v>17347.13855421687</v>
+      </c>
+      <c r="HJ3">
+        <v>61276.03125</v>
+      </c>
+      <c r="HK3">
+        <v>52522.3125</v>
+      </c>
+      <c r="HL3">
+        <v>32513.8125</v>
+      </c>
+      <c r="HM3">
+        <v>140059.5</v>
+      </c>
+      <c r="HN3">
+        <v>51271.78125</v>
+      </c>
+      <c r="HO3">
+        <v>67528.6875</v>
+      </c>
+      <c r="HP3">
+        <v>67528.6875</v>
+      </c>
+      <c r="HQ3">
+        <v>63777.09375</v>
+      </c>
+      <c r="HR3">
+        <v>40017</v>
+      </c>
+      <c r="HS3">
+        <v>127554.1875</v>
+      </c>
+      <c r="HT3">
+        <v>76282.40625</v>
+      </c>
+      <c r="HU3">
+        <v>51271.78125</v>
+      </c>
+      <c r="HV3">
+        <v>49000.61728395062</v>
+      </c>
+      <c r="HW3">
+        <v>27440.34567901234</v>
+      </c>
+      <c r="HX3">
+        <v>34300.43209876543</v>
+      </c>
+      <c r="HY3">
+        <v>79381</v>
+      </c>
+      <c r="HZ3">
+        <v>42140.53086419753</v>
+      </c>
+      <c r="IA3">
+        <v>52920.66666666666</v>
+      </c>
+      <c r="IB3">
+        <v>44100.55555555555</v>
+      </c>
+      <c r="IC3">
+        <v>45080.56790123456</v>
+      </c>
+      <c r="ID3">
+        <v>32340.40740740741</v>
+      </c>
+      <c r="IE3">
+        <v>73500.92592592593</v>
+      </c>
+      <c r="IF3">
+        <v>46060.58024691358</v>
+      </c>
+      <c r="IG3">
+        <v>47040.59259259259</v>
+      </c>
+      <c r="IH3">
+        <v>124908.1646341463</v>
+      </c>
+      <c r="II3">
+        <v>70893.82317073172</v>
+      </c>
+      <c r="IJ3">
+        <v>55139.64024390245</v>
+      </c>
+      <c r="IK3">
+        <v>50638.44512195123</v>
+      </c>
+      <c r="IL3">
+        <v>30383.06707317074</v>
+      </c>
+      <c r="IM3">
+        <v>33758.96341463415</v>
+      </c>
+      <c r="IN3">
+        <v>115905.7743902439</v>
+      </c>
+      <c r="IO3">
+        <v>115905.7743902439</v>
+      </c>
+      <c r="IP3">
+        <v>66392.62804878049</v>
+      </c>
+      <c r="IQ3">
+        <v>51763.74390243903</v>
+      </c>
+      <c r="IR3">
+        <v>38260.15853658537</v>
+      </c>
+      <c r="IS3">
+        <v>22505.9756097561</v>
+      </c>
+      <c r="IT3">
+        <v>61122.57851239669</v>
+      </c>
+      <c r="IU3">
+        <v>43823.73553719008</v>
+      </c>
+      <c r="IV3">
+        <v>32291.17355371901</v>
+      </c>
+      <c r="IW3">
+        <v>53049.78512396694</v>
+      </c>
+      <c r="IX3">
+        <v>27678.14876033058</v>
+      </c>
+      <c r="IY3">
+        <v>33444.42975206611</v>
+      </c>
+      <c r="IZ3">
+        <v>47283.50413223141</v>
+      </c>
+      <c r="JA3">
+        <v>53049.78512396695</v>
+      </c>
+      <c r="JB3">
+        <v>33444.42975206612</v>
+      </c>
+      <c r="JC3">
+        <v>54203.04132231405</v>
+      </c>
+      <c r="JD3">
+        <v>36904.19834710743</v>
+      </c>
+      <c r="JE3">
+        <v>25371.63636363636</v>
+      </c>
+      <c r="JF3">
+        <v>12476.0245398773</v>
+      </c>
+      <c r="JG3">
+        <v>11908.93251533742</v>
+      </c>
+      <c r="JH3">
+        <v>11341.84049079755</v>
+      </c>
+      <c r="JI3">
+        <v>31190.06134969325</v>
+      </c>
+      <c r="JJ3">
+        <v>12476.0245398773</v>
+      </c>
+      <c r="JK3">
+        <v>17863.39877300613</v>
+      </c>
+      <c r="JL3">
+        <v>19281.12883435583</v>
+      </c>
+      <c r="JM3">
+        <v>12759.57055214724</v>
+      </c>
+      <c r="JN3">
+        <v>10207.65644171779</v>
+      </c>
+      <c r="JO3">
+        <v>32607.79141104294</v>
+      </c>
+      <c r="JP3">
+        <v>16162.1226993865</v>
+      </c>
+      <c r="JQ3">
+        <v>15311.48466257669</v>
+      </c>
+      <c r="JR3">
+        <v>38316</v>
+      </c>
+      <c r="JS3">
+        <v>28428</v>
+      </c>
+      <c r="JT3">
+        <v>16892</v>
+      </c>
+      <c r="JU3">
+        <v>46555.99999999999</v>
+      </c>
+      <c r="JV3">
+        <v>21012</v>
+      </c>
+      <c r="JW3">
+        <v>20188</v>
+      </c>
+      <c r="JX3">
+        <v>48615.99999999999</v>
+      </c>
+      <c r="JY3">
+        <v>33784</v>
+      </c>
+      <c r="JZ3">
+        <v>18540</v>
+      </c>
+      <c r="KA3">
+        <v>49027.99999999999</v>
+      </c>
+      <c r="KB3">
+        <v>32136</v>
+      </c>
+      <c r="KC3">
+        <v>21012</v>
+      </c>
+      <c r="KD3">
+        <v>31828.71812080537</v>
+      </c>
+      <c r="KE3">
+        <v>19420.91275167785</v>
+      </c>
+      <c r="KF3">
+        <v>16184.09395973154</v>
+      </c>
+      <c r="KG3">
+        <v>26973.48993288591</v>
+      </c>
+      <c r="KH3">
+        <v>12407.80536912752</v>
+      </c>
+      <c r="KI3">
+        <v>27512.95973154362</v>
+      </c>
+      <c r="KJ3">
+        <v>25894.55033557047</v>
+      </c>
+      <c r="KK3">
+        <v>16723.56375838926</v>
+      </c>
+      <c r="KL3">
+        <v>17263.03355704698</v>
+      </c>
+      <c r="KM3">
+        <v>32907.6577181208</v>
+      </c>
+      <c r="KN3">
+        <v>14565.68456375839</v>
+      </c>
+      <c r="KO3">
+        <v>30210.30872483222</v>
+      </c>
+      <c r="KP3">
+        <v>16413.18238993711</v>
+      </c>
+      <c r="KQ3">
+        <v>8719.503144654089</v>
+      </c>
+      <c r="KR3">
+        <v>11284.06289308176</v>
+      </c>
+      <c r="KS3">
+        <v>67191.46540880503</v>
+      </c>
+      <c r="KT3">
+        <v>26158.50943396226</v>
+      </c>
+      <c r="KU3">
+        <v>30774.71698113207</v>
+      </c>
+      <c r="KV3">
+        <v>8719.503144654089</v>
+      </c>
+      <c r="KW3">
+        <v>9745.327044025158</v>
+      </c>
+      <c r="KX3">
+        <v>8206.591194968554</v>
+      </c>
+      <c r="KY3">
+        <v>73346.40880503145</v>
+      </c>
+      <c r="KZ3">
+        <v>40007.13207547169</v>
+      </c>
+      <c r="LA3">
+        <v>23081.03773584906</v>
+      </c>
+      <c r="LB3">
+        <v>15794.25641025641</v>
+      </c>
+      <c r="LC3">
+        <v>11098.66666666666</v>
+      </c>
+      <c r="LD3">
+        <v>5976.205128205127</v>
+      </c>
+      <c r="LE3">
+        <v>73848.82051282052</v>
+      </c>
+      <c r="LF3">
+        <v>28600.41025641025</v>
+      </c>
+      <c r="LG3">
+        <v>21770.46153846154</v>
+      </c>
+      <c r="LH3">
+        <v>17928.61538461538</v>
+      </c>
+      <c r="LI3">
+        <v>13659.89743589743</v>
+      </c>
+      <c r="LJ3">
+        <v>7256.820512820512</v>
+      </c>
+      <c r="LK3">
+        <v>72141.33333333333</v>
+      </c>
+      <c r="LL3">
+        <v>38845.33333333333</v>
+      </c>
+      <c r="LM3">
+        <v>23477.94871794872</v>
+      </c>
+      <c r="LN3">
+        <v>9256.000000000002</v>
+      </c>
+      <c r="LO3">
+        <v>3239.600000000001</v>
+      </c>
+      <c r="LP3">
+        <v>3702.400000000001</v>
+      </c>
+      <c r="LQ3">
+        <v>38643.8</v>
+      </c>
+      <c r="LR3">
+        <v>15619.5</v>
+      </c>
+      <c r="LS3">
+        <v>13536.9</v>
+      </c>
+      <c r="LT3">
+        <v>8677.500000000002</v>
+      </c>
+      <c r="LU3">
+        <v>3586.700000000001</v>
+      </c>
+      <c r="LV3">
+        <v>4628.000000000001</v>
+      </c>
+      <c r="LW3">
+        <v>32280.3</v>
+      </c>
+      <c r="LX3">
+        <v>20941.7</v>
+      </c>
+      <c r="LY3">
+        <v>15850.9</v>
+      </c>
+      <c r="LZ3">
+        <v>10570.31055900621</v>
+      </c>
+      <c r="MA3">
+        <v>10570.31055900621</v>
+      </c>
+      <c r="MB3">
+        <v>6870.701863354038</v>
+      </c>
+      <c r="MC3">
+        <v>46509.36645962734</v>
+      </c>
+      <c r="MD3">
+        <v>19026.55900621118</v>
+      </c>
+      <c r="ME3">
+        <v>30653.90062111802</v>
+      </c>
+      <c r="MF3">
+        <v>9513.27950310559</v>
+      </c>
+      <c r="MG3">
+        <v>5813.670807453416</v>
+      </c>
+      <c r="MH3">
+        <v>7927.732919254659</v>
+      </c>
+      <c r="MI3">
+        <v>49151.94409937889</v>
+      </c>
+      <c r="MJ3">
+        <v>21140.62111801242</v>
+      </c>
+      <c r="MK3">
+        <v>24311.71428571429</v>
+      </c>
+      <c r="ML3">
+        <v>19865</v>
+      </c>
+      <c r="MM3">
+        <v>23975</v>
+      </c>
+      <c r="MN3">
+        <v>21235</v>
+      </c>
+      <c r="MO3">
+        <v>28769.99999999999</v>
+      </c>
+      <c r="MP3">
+        <v>24660</v>
+      </c>
+      <c r="MQ3">
+        <v>25345</v>
+      </c>
+      <c r="MR3">
+        <v>31510</v>
+      </c>
+      <c r="MS3">
+        <v>26715</v>
+      </c>
+      <c r="MT3">
+        <v>14385</v>
+      </c>
+      <c r="MU3">
+        <v>29454.99999999999</v>
+      </c>
+      <c r="MV3">
+        <v>22605</v>
+      </c>
+      <c r="MW3">
+        <v>25345</v>
+      </c>
+      <c r="MX3">
+        <v>70243.71428571428</v>
+      </c>
+      <c r="MY3">
+        <v>47847.16770186335</v>
+      </c>
+      <c r="MZ3">
+        <v>33594.8198757764</v>
+      </c>
+      <c r="NA3">
+        <v>130307.1801242236</v>
+      </c>
+      <c r="NB3">
+        <v>76351.86335403727</v>
+      </c>
+      <c r="NC3">
+        <v>57009.39130434782</v>
+      </c>
+      <c r="ND3">
+        <v>74315.81366459627</v>
+      </c>
+      <c r="NE3">
+        <v>63117.5403726708</v>
+      </c>
+      <c r="NF3">
+        <v>22396.54658385093</v>
+      </c>
+      <c r="NG3">
+        <v>94676.3105590062</v>
+      </c>
+      <c r="NH3">
+        <v>72279.76397515528</v>
+      </c>
+      <c r="NI3">
+        <v>41739.01863354037</v>
+      </c>
+      <c r="NJ3">
+        <v>23680.71951219512</v>
+      </c>
+      <c r="NK3">
+        <v>16504.74390243902</v>
+      </c>
+      <c r="NL3">
+        <v>18657.53658536585</v>
+      </c>
+      <c r="NM3">
+        <v>60278.19512195121</v>
+      </c>
+      <c r="NN3">
+        <v>33727.08536585366</v>
+      </c>
+      <c r="NO3">
+        <v>32291.89024390244</v>
+      </c>
+      <c r="NP3">
+        <v>25833.51219512195</v>
+      </c>
+      <c r="NQ3">
+        <v>17939.93902439024</v>
+      </c>
+      <c r="NR3">
+        <v>20092.73170731707</v>
+      </c>
+      <c r="NS3">
+        <v>48079.03658536585</v>
+      </c>
+      <c r="NT3">
+        <v>34444.68292682926</v>
+      </c>
+      <c r="NU3">
+        <v>42338.25609756097</v>
+      </c>
+      <c r="NV3">
+        <v>32630.73825503356</v>
+      </c>
+      <c r="NW3">
+        <v>31905.61073825504</v>
+      </c>
+      <c r="NX3">
+        <v>16677.93288590604</v>
+      </c>
+      <c r="NY3">
+        <v>47858.41610738255</v>
+      </c>
+      <c r="NZ3">
+        <v>20303.57046979865</v>
+      </c>
+      <c r="OA3">
+        <v>37706.63087248322</v>
+      </c>
+      <c r="OB3">
+        <v>39156.88590604027</v>
+      </c>
+      <c r="OC3">
+        <v>14502.55033557047</v>
+      </c>
+      <c r="OD3">
+        <v>19578.44295302013</v>
+      </c>
+      <c r="OE3">
+        <v>57285.07382550335</v>
+      </c>
+      <c r="OF3">
+        <v>25379.46308724832</v>
+      </c>
+      <c r="OG3">
+        <v>39882.01342281879</v>
+      </c>
+      <c r="OH3">
+        <v>18126.97435897436</v>
+      </c>
+      <c r="OI3">
+        <v>13833.74358974359</v>
+      </c>
+      <c r="OJ3">
+        <v>10971.58974358974</v>
+      </c>
+      <c r="OK3">
+        <v>22897.23076923077</v>
+      </c>
+      <c r="OL3">
+        <v>17172.92307692307</v>
+      </c>
+      <c r="OM3">
+        <v>14310.76923076923</v>
+      </c>
+      <c r="ON3">
+        <v>14787.79487179487</v>
+      </c>
+      <c r="OO3">
+        <v>19081.02564102564</v>
+      </c>
+      <c r="OP3">
+        <v>11925.64102564103</v>
+      </c>
+      <c r="OQ3">
+        <v>19081.02564102564</v>
+      </c>
+      <c r="OR3">
+        <v>15264.82051282051</v>
+      </c>
+      <c r="OS3">
+        <v>19081.02564102564</v>
+      </c>
+      <c r="OT3">
+        <v>58632.72727272727</v>
+      </c>
+      <c r="OU3">
+        <v>21987.27272727273</v>
+      </c>
+      <c r="OV3">
+        <v>20521.45454545454</v>
+      </c>
+      <c r="OW3">
+        <v>206680.3636363636</v>
+      </c>
+      <c r="OX3">
+        <v>131923.6363636364</v>
+      </c>
+      <c r="OY3">
+        <v>105538.9090909091</v>
+      </c>
+      <c r="OZ3">
+        <v>48372</v>
+      </c>
+      <c r="PA3">
+        <v>30782.18181818182</v>
+      </c>
+      <c r="PB3">
+        <v>30782.18181818182</v>
+      </c>
+      <c r="PC3">
+        <v>177364</v>
+      </c>
+      <c r="PD3">
+        <v>134855.2727272727</v>
+      </c>
+      <c r="PE3">
+        <v>102607.2727272727</v>
+      </c>
+      <c r="PF3">
+        <v>46323.9477124183</v>
+      </c>
+      <c r="PG3">
+        <v>36941.88235294117</v>
+      </c>
+      <c r="PH3">
+        <v>23455.16339869281</v>
+      </c>
+      <c r="PI3">
+        <v>45737.56862745097</v>
+      </c>
+      <c r="PJ3">
+        <v>26387.05882352941</v>
+      </c>
+      <c r="PK3">
+        <v>19350.50980392157</v>
+      </c>
+      <c r="PL3">
+        <v>49255.84313725489</v>
+      </c>
+      <c r="PM3">
+        <v>40460.15686274509</v>
+      </c>
+      <c r="PN3">
+        <v>24041.54248366013</v>
+      </c>
+      <c r="PO3">
+        <v>50428.60130718954</v>
+      </c>
+      <c r="PP3">
+        <v>30491.71241830065</v>
+      </c>
+      <c r="PQ3">
+        <v>21109.64705882352</v>
+      </c>
+      <c r="PR3">
+        <v>29028.24427480916</v>
+      </c>
+      <c r="PS3">
+        <v>13194.65648854962</v>
+      </c>
+      <c r="PT3">
+        <v>9236.259541984733</v>
+      </c>
+      <c r="PU3">
+        <v>59375.95419847329</v>
+      </c>
+      <c r="PV3">
+        <v>22430.91603053435</v>
+      </c>
+      <c r="PW3">
+        <v>36945.03816793893</v>
+      </c>
+      <c r="PX3">
+        <v>29028.24427480916</v>
+      </c>
+      <c r="PY3">
+        <v>22430.91603053435</v>
+      </c>
+      <c r="PZ3">
+        <v>19791.98473282443</v>
+      </c>
+      <c r="QA3">
+        <v>48160.49618320611</v>
+      </c>
+      <c r="QB3">
+        <v>32326.90839694657</v>
+      </c>
+      <c r="QC3">
+        <v>39583.96946564886</v>
+      </c>
+      <c r="QD3">
+        <v>20450740.2356909</v>
       </c>
     </row>
   </sheetData>
